--- a/reports/upset_high_seeds.xlsx
+++ b/reports/upset_high_seeds.xlsx
@@ -549,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>169 games (First Four not included). November = the team's games in November of that season. Top 40 = that season's pre-tournament top 40 by Strongside net rating; record from games before the tournament.</t>
+          <t>169 games (First Four not included). November = the team's games in November of that season. Top 40 = that season's pre-tournament top 40 by Strongside net rating; the top-40 record counts November games only.</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>No games vs top 40 (not battle tested)</t>
+          <t>No November games vs top 40 (not battle tested)</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -628,22 +628,22 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Top-40 W</t>
+          <t>Nov top-40 W</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Top-40 L</t>
+          <t>Nov top-40 L</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>Record vs top 40</t>
+          <t>November record vs top 40</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>Top-40 games</t>
+          <t>Nov top-40 games</t>
         </is>
       </c>
     </row>
@@ -688,10 +688,10 @@
         <v/>
       </c>
       <c r="K6" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M6" s="8">
         <f>K6&amp;"-"&amp;L6</f>
@@ -743,10 +743,10 @@
         <v/>
       </c>
       <c r="K7" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="8">
         <f>K7&amp;"-"&amp;L7</f>
@@ -798,10 +798,10 @@
         <v/>
       </c>
       <c r="K8" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="8">
         <f>K8&amp;"-"&amp;L8</f>
@@ -853,10 +853,10 @@
         <v/>
       </c>
       <c r="K9" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M9" s="8">
         <f>K9&amp;"-"&amp;L9</f>
@@ -908,10 +908,10 @@
         <v/>
       </c>
       <c r="K10" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M10" s="8">
         <f>K10&amp;"-"&amp;L10</f>
@@ -963,10 +963,10 @@
         <v/>
       </c>
       <c r="K11" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="8">
         <f>K11&amp;"-"&amp;L11</f>
@@ -1018,10 +1018,10 @@
         <v/>
       </c>
       <c r="K12" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M12" s="8">
         <f>K12&amp;"-"&amp;L12</f>
@@ -1073,7 +1073,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L13" s="8" t="n">
         <v>0</v>
@@ -1128,10 +1128,10 @@
         <v/>
       </c>
       <c r="K14" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M14" s="8">
         <f>K14&amp;"-"&amp;L14</f>
@@ -1183,10 +1183,10 @@
         <v/>
       </c>
       <c r="K15" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M15" s="8">
         <f>K15&amp;"-"&amp;L15</f>
@@ -1238,10 +1238,10 @@
         <v/>
       </c>
       <c r="K16" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M16" s="8">
         <f>K16&amp;"-"&amp;L16</f>
@@ -1293,10 +1293,10 @@
         <v/>
       </c>
       <c r="K17" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M17" s="8">
         <f>K17&amp;"-"&amp;L17</f>
@@ -1348,10 +1348,10 @@
         <v/>
       </c>
       <c r="K18" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M18" s="8">
         <f>K18&amp;"-"&amp;L18</f>
@@ -1403,10 +1403,10 @@
         <v/>
       </c>
       <c r="K19" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M19" s="8">
         <f>K19&amp;"-"&amp;L19</f>
@@ -1458,10 +1458,10 @@
         <v/>
       </c>
       <c r="K20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M20" s="8">
         <f>K20&amp;"-"&amp;L20</f>
@@ -1513,10 +1513,10 @@
         <v/>
       </c>
       <c r="K21" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M21" s="8">
         <f>K21&amp;"-"&amp;L21</f>
@@ -1568,10 +1568,10 @@
         <v/>
       </c>
       <c r="K22" s="8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M22" s="8">
         <f>K22&amp;"-"&amp;L22</f>
@@ -1623,10 +1623,10 @@
         <v/>
       </c>
       <c r="K23" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M23" s="8">
         <f>K23&amp;"-"&amp;L23</f>
@@ -1678,10 +1678,10 @@
         <v/>
       </c>
       <c r="K24" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M24" s="8">
         <f>K24&amp;"-"&amp;L24</f>
@@ -1733,10 +1733,10 @@
         <v/>
       </c>
       <c r="K25" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M25" s="8">
         <f>K25&amp;"-"&amp;L25</f>
@@ -1788,10 +1788,10 @@
         <v/>
       </c>
       <c r="K26" s="8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M26" s="8">
         <f>K26&amp;"-"&amp;L26</f>
@@ -1843,10 +1843,10 @@
         <v/>
       </c>
       <c r="K27" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M27" s="8">
         <f>K27&amp;"-"&amp;L27</f>
@@ -1898,10 +1898,10 @@
         <v/>
       </c>
       <c r="K28" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" s="8">
         <f>K28&amp;"-"&amp;L28</f>
@@ -1953,10 +1953,10 @@
         <v/>
       </c>
       <c r="K29" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M29" s="8">
         <f>K29&amp;"-"&amp;L29</f>
@@ -2008,10 +2008,10 @@
         <v/>
       </c>
       <c r="K30" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M30" s="8">
         <f>K30&amp;"-"&amp;L30</f>
@@ -2063,10 +2063,10 @@
         <v/>
       </c>
       <c r="K31" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M31" s="8">
         <f>K31&amp;"-"&amp;L31</f>
@@ -2118,10 +2118,10 @@
         <v/>
       </c>
       <c r="K32" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M32" s="8">
         <f>K32&amp;"-"&amp;L32</f>
@@ -2173,10 +2173,10 @@
         <v/>
       </c>
       <c r="K33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="M33" s="8">
         <f>K33&amp;"-"&amp;L33</f>
@@ -2228,10 +2228,10 @@
         <v/>
       </c>
       <c r="K34" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="8">
         <f>K34&amp;"-"&amp;L34</f>
@@ -2283,10 +2283,10 @@
         <v/>
       </c>
       <c r="K35" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M35" s="8">
         <f>K35&amp;"-"&amp;L35</f>
@@ -2338,10 +2338,10 @@
         <v/>
       </c>
       <c r="K36" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M36" s="8">
         <f>K36&amp;"-"&amp;L36</f>
@@ -2393,10 +2393,10 @@
         <v/>
       </c>
       <c r="K37" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M37" s="8">
         <f>K37&amp;"-"&amp;L37</f>
@@ -2448,10 +2448,10 @@
         <v/>
       </c>
       <c r="K38" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M38" s="8">
         <f>K38&amp;"-"&amp;L38</f>
@@ -2503,10 +2503,10 @@
         <v/>
       </c>
       <c r="K39" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M39" s="8">
         <f>K39&amp;"-"&amp;L39</f>
@@ -2558,10 +2558,10 @@
         <v/>
       </c>
       <c r="K40" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M40" s="8">
         <f>K40&amp;"-"&amp;L40</f>
@@ -2613,10 +2613,10 @@
         <v/>
       </c>
       <c r="K41" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M41" s="8">
         <f>K41&amp;"-"&amp;L41</f>
@@ -2668,10 +2668,10 @@
         <v/>
       </c>
       <c r="K42" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M42" s="8">
         <f>K42&amp;"-"&amp;L42</f>
@@ -2723,10 +2723,10 @@
         <v/>
       </c>
       <c r="K43" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L43" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M43" s="8">
         <f>K43&amp;"-"&amp;L43</f>
@@ -2778,10 +2778,10 @@
         <v/>
       </c>
       <c r="K44" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M44" s="8">
         <f>K44&amp;"-"&amp;L44</f>
@@ -2833,10 +2833,10 @@
         <v/>
       </c>
       <c r="K45" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" s="8">
         <f>K45&amp;"-"&amp;L45</f>
@@ -2888,10 +2888,10 @@
         <v/>
       </c>
       <c r="K46" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="8">
         <f>K46&amp;"-"&amp;L46</f>
@@ -2943,7 +2943,7 @@
         <v/>
       </c>
       <c r="K47" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L47" s="8" t="n">
         <v>1</v>
@@ -2998,10 +2998,10 @@
         <v/>
       </c>
       <c r="K48" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M48" s="8">
         <f>K48&amp;"-"&amp;L48</f>
@@ -3053,10 +3053,10 @@
         <v/>
       </c>
       <c r="K49" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M49" s="8">
         <f>K49&amp;"-"&amp;L49</f>
@@ -3108,10 +3108,10 @@
         <v/>
       </c>
       <c r="K50" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M50" s="8">
         <f>K50&amp;"-"&amp;L50</f>
@@ -3163,10 +3163,10 @@
         <v/>
       </c>
       <c r="K51" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M51" s="8">
         <f>K51&amp;"-"&amp;L51</f>
@@ -3218,10 +3218,10 @@
         <v/>
       </c>
       <c r="K52" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M52" s="8">
         <f>K52&amp;"-"&amp;L52</f>
@@ -3273,10 +3273,10 @@
         <v/>
       </c>
       <c r="K53" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" s="8">
         <f>K53&amp;"-"&amp;L53</f>
@@ -3328,10 +3328,10 @@
         <v/>
       </c>
       <c r="K54" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M54" s="8">
         <f>K54&amp;"-"&amp;L54</f>
@@ -3383,10 +3383,10 @@
         <v/>
       </c>
       <c r="K55" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M55" s="8">
         <f>K55&amp;"-"&amp;L55</f>
@@ -3438,7 +3438,7 @@
         <v/>
       </c>
       <c r="K56" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="8" t="n">
         <v>0</v>
@@ -3493,10 +3493,10 @@
         <v/>
       </c>
       <c r="K57" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M57" s="8">
         <f>K57&amp;"-"&amp;L57</f>
@@ -3548,10 +3548,10 @@
         <v/>
       </c>
       <c r="K58" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L58" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M58" s="8">
         <f>K58&amp;"-"&amp;L58</f>
@@ -3603,10 +3603,10 @@
         <v/>
       </c>
       <c r="K59" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L59" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" s="8">
         <f>K59&amp;"-"&amp;L59</f>
@@ -3658,10 +3658,10 @@
         <v/>
       </c>
       <c r="K60" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L60" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M60" s="8">
         <f>K60&amp;"-"&amp;L60</f>
@@ -3713,10 +3713,10 @@
         <v/>
       </c>
       <c r="K61" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M61" s="8">
         <f>K61&amp;"-"&amp;L61</f>
@@ -3768,10 +3768,10 @@
         <v/>
       </c>
       <c r="K62" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L62" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M62" s="8">
         <f>K62&amp;"-"&amp;L62</f>
@@ -3823,10 +3823,10 @@
         <v/>
       </c>
       <c r="K63" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L63" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" s="8">
         <f>K63&amp;"-"&amp;L63</f>
@@ -3878,10 +3878,10 @@
         <v/>
       </c>
       <c r="K64" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L64" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M64" s="8">
         <f>K64&amp;"-"&amp;L64</f>
@@ -3933,10 +3933,10 @@
         <v/>
       </c>
       <c r="K65" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L65" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M65" s="8">
         <f>K65&amp;"-"&amp;L65</f>
@@ -3988,10 +3988,10 @@
         <v/>
       </c>
       <c r="K66" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L66" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M66" s="8">
         <f>K66&amp;"-"&amp;L66</f>
@@ -4098,10 +4098,10 @@
         <v/>
       </c>
       <c r="K68" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L68" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M68" s="8">
         <f>K68&amp;"-"&amp;L68</f>
@@ -4153,10 +4153,10 @@
         <v/>
       </c>
       <c r="K69" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L69" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="8">
         <f>K69&amp;"-"&amp;L69</f>
@@ -4208,10 +4208,10 @@
         <v/>
       </c>
       <c r="K70" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L70" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M70" s="8">
         <f>K70&amp;"-"&amp;L70</f>
@@ -4263,10 +4263,10 @@
         <v/>
       </c>
       <c r="K71" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L71" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M71" s="8">
         <f>K71&amp;"-"&amp;L71</f>
@@ -4318,10 +4318,10 @@
         <v/>
       </c>
       <c r="K72" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L72" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M72" s="8">
         <f>K72&amp;"-"&amp;L72</f>
@@ -4373,10 +4373,10 @@
         <v/>
       </c>
       <c r="K73" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L73" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M73" s="8">
         <f>K73&amp;"-"&amp;L73</f>
@@ -4428,10 +4428,10 @@
         <v/>
       </c>
       <c r="K74" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L74" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M74" s="8">
         <f>K74&amp;"-"&amp;L74</f>
@@ -4483,10 +4483,10 @@
         <v/>
       </c>
       <c r="K75" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L75" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M75" s="8">
         <f>K75&amp;"-"&amp;L75</f>
@@ -4538,10 +4538,10 @@
         <v/>
       </c>
       <c r="K76" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L76" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M76" s="8">
         <f>K76&amp;"-"&amp;L76</f>
@@ -4593,10 +4593,10 @@
         <v/>
       </c>
       <c r="K77" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L77" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M77" s="8">
         <f>K77&amp;"-"&amp;L77</f>
@@ -4648,10 +4648,10 @@
         <v/>
       </c>
       <c r="K78" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L78" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M78" s="8">
         <f>K78&amp;"-"&amp;L78</f>
@@ -4703,10 +4703,10 @@
         <v/>
       </c>
       <c r="K79" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M79" s="8">
         <f>K79&amp;"-"&amp;L79</f>
@@ -4758,10 +4758,10 @@
         <v/>
       </c>
       <c r="K80" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L80" s="8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M80" s="8">
         <f>K80&amp;"-"&amp;L80</f>
@@ -4813,10 +4813,10 @@
         <v/>
       </c>
       <c r="K81" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L81" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M81" s="8">
         <f>K81&amp;"-"&amp;L81</f>
@@ -4868,10 +4868,10 @@
         <v/>
       </c>
       <c r="K82" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L82" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M82" s="8">
         <f>K82&amp;"-"&amp;L82</f>
@@ -4923,10 +4923,10 @@
         <v/>
       </c>
       <c r="K83" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L83" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M83" s="8">
         <f>K83&amp;"-"&amp;L83</f>
@@ -4978,10 +4978,10 @@
         <v/>
       </c>
       <c r="K84" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L84" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M84" s="8">
         <f>K84&amp;"-"&amp;L84</f>
@@ -5033,10 +5033,10 @@
         <v/>
       </c>
       <c r="K85" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L85" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M85" s="8">
         <f>K85&amp;"-"&amp;L85</f>
@@ -5088,10 +5088,10 @@
         <v/>
       </c>
       <c r="K86" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L86" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M86" s="8">
         <f>K86&amp;"-"&amp;L86</f>
@@ -5143,10 +5143,10 @@
         <v/>
       </c>
       <c r="K87" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L87" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M87" s="8">
         <f>K87&amp;"-"&amp;L87</f>
@@ -5198,10 +5198,10 @@
         <v/>
       </c>
       <c r="K88" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L88" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M88" s="8">
         <f>K88&amp;"-"&amp;L88</f>
@@ -5253,10 +5253,10 @@
         <v/>
       </c>
       <c r="K89" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L89" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M89" s="8">
         <f>K89&amp;"-"&amp;L89</f>
@@ -5308,10 +5308,10 @@
         <v/>
       </c>
       <c r="K90" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L90" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M90" s="8">
         <f>K90&amp;"-"&amp;L90</f>
@@ -5363,10 +5363,10 @@
         <v/>
       </c>
       <c r="K91" s="8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L91" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M91" s="8">
         <f>K91&amp;"-"&amp;L91</f>
@@ -5418,10 +5418,10 @@
         <v/>
       </c>
       <c r="K92" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L92" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M92" s="8">
         <f>K92&amp;"-"&amp;L92</f>
@@ -5473,10 +5473,10 @@
         <v/>
       </c>
       <c r="K93" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L93" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M93" s="8">
         <f>K93&amp;"-"&amp;L93</f>
@@ -5528,10 +5528,10 @@
         <v/>
       </c>
       <c r="K94" s="8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L94" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94" s="8">
         <f>K94&amp;"-"&amp;L94</f>
@@ -5583,7 +5583,7 @@
         <v/>
       </c>
       <c r="K95" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L95" s="8" t="n">
         <v>2</v>
@@ -5638,10 +5638,10 @@
         <v/>
       </c>
       <c r="K96" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L96" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M96" s="8">
         <f>K96&amp;"-"&amp;L96</f>
@@ -5693,10 +5693,10 @@
         <v/>
       </c>
       <c r="K97" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L97" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M97" s="8">
         <f>K97&amp;"-"&amp;L97</f>
@@ -5748,10 +5748,10 @@
         <v/>
       </c>
       <c r="K98" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L98" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M98" s="8">
         <f>K98&amp;"-"&amp;L98</f>
@@ -5803,10 +5803,10 @@
         <v/>
       </c>
       <c r="K99" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L99" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M99" s="8">
         <f>K99&amp;"-"&amp;L99</f>
@@ -5858,10 +5858,10 @@
         <v/>
       </c>
       <c r="K100" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L100" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M100" s="8">
         <f>K100&amp;"-"&amp;L100</f>
@@ -5913,10 +5913,10 @@
         <v/>
       </c>
       <c r="K101" s="8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L101" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M101" s="8">
         <f>K101&amp;"-"&amp;L101</f>
@@ -5968,10 +5968,10 @@
         <v/>
       </c>
       <c r="K102" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L102" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M102" s="8">
         <f>K102&amp;"-"&amp;L102</f>
@@ -6023,10 +6023,10 @@
         <v/>
       </c>
       <c r="K103" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L103" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M103" s="8">
         <f>K103&amp;"-"&amp;L103</f>
@@ -6078,10 +6078,10 @@
         <v/>
       </c>
       <c r="K104" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L104" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M104" s="8">
         <f>K104&amp;"-"&amp;L104</f>
@@ -6133,10 +6133,10 @@
         <v/>
       </c>
       <c r="K105" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L105" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M105" s="8">
         <f>K105&amp;"-"&amp;L105</f>
@@ -6191,7 +6191,7 @@
         <v>0</v>
       </c>
       <c r="L106" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M106" s="8">
         <f>K106&amp;"-"&amp;L106</f>
@@ -6243,10 +6243,10 @@
         <v/>
       </c>
       <c r="K107" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L107" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M107" s="8">
         <f>K107&amp;"-"&amp;L107</f>
@@ -6298,10 +6298,10 @@
         <v/>
       </c>
       <c r="K108" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L108" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M108" s="8">
         <f>K108&amp;"-"&amp;L108</f>
@@ -6353,10 +6353,10 @@
         <v/>
       </c>
       <c r="K109" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L109" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M109" s="8">
         <f>K109&amp;"-"&amp;L109</f>
@@ -6408,10 +6408,10 @@
         <v/>
       </c>
       <c r="K110" s="8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L110" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M110" s="8">
         <f>K110&amp;"-"&amp;L110</f>
@@ -6463,10 +6463,10 @@
         <v/>
       </c>
       <c r="K111" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L111" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M111" s="8">
         <f>K111&amp;"-"&amp;L111</f>
@@ -6518,10 +6518,10 @@
         <v/>
       </c>
       <c r="K112" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L112" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M112" s="8">
         <f>K112&amp;"-"&amp;L112</f>
@@ -6573,10 +6573,10 @@
         <v/>
       </c>
       <c r="K113" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L113" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M113" s="8">
         <f>K113&amp;"-"&amp;L113</f>
@@ -6628,10 +6628,10 @@
         <v/>
       </c>
       <c r="K114" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L114" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M114" s="8">
         <f>K114&amp;"-"&amp;L114</f>
@@ -6683,10 +6683,10 @@
         <v/>
       </c>
       <c r="K115" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L115" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M115" s="8">
         <f>K115&amp;"-"&amp;L115</f>
@@ -6738,10 +6738,10 @@
         <v/>
       </c>
       <c r="K116" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L116" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M116" s="8">
         <f>K116&amp;"-"&amp;L116</f>
@@ -6793,10 +6793,10 @@
         <v/>
       </c>
       <c r="K117" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L117" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M117" s="8">
         <f>K117&amp;"-"&amp;L117</f>
@@ -6851,7 +6851,7 @@
         <v>1</v>
       </c>
       <c r="L118" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" s="8">
         <f>K118&amp;"-"&amp;L118</f>
@@ -6903,10 +6903,10 @@
         <v/>
       </c>
       <c r="K119" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M119" s="8">
         <f>K119&amp;"-"&amp;L119</f>
@@ -6958,10 +6958,10 @@
         <v/>
       </c>
       <c r="K120" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L120" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M120" s="8">
         <f>K120&amp;"-"&amp;L120</f>
@@ -7013,10 +7013,10 @@
         <v/>
       </c>
       <c r="K121" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L121" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M121" s="8">
         <f>K121&amp;"-"&amp;L121</f>
@@ -7068,10 +7068,10 @@
         <v/>
       </c>
       <c r="K122" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L122" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M122" s="8">
         <f>K122&amp;"-"&amp;L122</f>
@@ -7123,10 +7123,10 @@
         <v/>
       </c>
       <c r="K123" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L123" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M123" s="8">
         <f>K123&amp;"-"&amp;L123</f>
@@ -7178,10 +7178,10 @@
         <v/>
       </c>
       <c r="K124" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L124" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M124" s="8">
         <f>K124&amp;"-"&amp;L124</f>
@@ -7233,10 +7233,10 @@
         <v/>
       </c>
       <c r="K125" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L125" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M125" s="8">
         <f>K125&amp;"-"&amp;L125</f>
@@ -7291,7 +7291,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" s="8">
         <f>K126&amp;"-"&amp;L126</f>
@@ -7343,10 +7343,10 @@
         <v/>
       </c>
       <c r="K127" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L127" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M127" s="8">
         <f>K127&amp;"-"&amp;L127</f>
@@ -7398,10 +7398,10 @@
         <v/>
       </c>
       <c r="K128" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L128" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M128" s="8">
         <f>K128&amp;"-"&amp;L128</f>
@@ -7453,10 +7453,10 @@
         <v/>
       </c>
       <c r="K129" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L129" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M129" s="8">
         <f>K129&amp;"-"&amp;L129</f>
@@ -7508,10 +7508,10 @@
         <v/>
       </c>
       <c r="K130" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L130" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M130" s="8">
         <f>K130&amp;"-"&amp;L130</f>
@@ -7563,10 +7563,10 @@
         <v/>
       </c>
       <c r="K131" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L131" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M131" s="8">
         <f>K131&amp;"-"&amp;L131</f>
@@ -7618,10 +7618,10 @@
         <v/>
       </c>
       <c r="K132" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L132" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M132" s="8">
         <f>K132&amp;"-"&amp;L132</f>
@@ -7673,10 +7673,10 @@
         <v/>
       </c>
       <c r="K133" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L133" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M133" s="8">
         <f>K133&amp;"-"&amp;L133</f>
@@ -7728,10 +7728,10 @@
         <v/>
       </c>
       <c r="K134" s="8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L134" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M134" s="8">
         <f>K134&amp;"-"&amp;L134</f>
@@ -7783,10 +7783,10 @@
         <v/>
       </c>
       <c r="K135" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L135" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M135" s="8">
         <f>K135&amp;"-"&amp;L135</f>
@@ -7838,10 +7838,10 @@
         <v/>
       </c>
       <c r="K136" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L136" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M136" s="8">
         <f>K136&amp;"-"&amp;L136</f>
@@ -7893,10 +7893,10 @@
         <v/>
       </c>
       <c r="K137" s="8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L137" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M137" s="8">
         <f>K137&amp;"-"&amp;L137</f>
@@ -7948,10 +7948,10 @@
         <v/>
       </c>
       <c r="K138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" s="8">
         <f>K138&amp;"-"&amp;L138</f>
@@ -8003,10 +8003,10 @@
         <v/>
       </c>
       <c r="K139" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L139" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M139" s="8">
         <f>K139&amp;"-"&amp;L139</f>
@@ -8058,10 +8058,10 @@
         <v/>
       </c>
       <c r="K140" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L140" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M140" s="8">
         <f>K140&amp;"-"&amp;L140</f>
@@ -8113,10 +8113,10 @@
         <v/>
       </c>
       <c r="K141" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L141" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M141" s="8">
         <f>K141&amp;"-"&amp;L141</f>
@@ -8168,10 +8168,10 @@
         <v/>
       </c>
       <c r="K142" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L142" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M142" s="8">
         <f>K142&amp;"-"&amp;L142</f>
@@ -8223,10 +8223,10 @@
         <v/>
       </c>
       <c r="K143" s="8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L143" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M143" s="8">
         <f>K143&amp;"-"&amp;L143</f>
@@ -8278,10 +8278,10 @@
         <v/>
       </c>
       <c r="K144" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L144" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" s="8">
         <f>K144&amp;"-"&amp;L144</f>
@@ -8333,10 +8333,10 @@
         <v/>
       </c>
       <c r="K145" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L145" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M145" s="8">
         <f>K145&amp;"-"&amp;L145</f>
@@ -8388,10 +8388,10 @@
         <v/>
       </c>
       <c r="K146" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L146" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M146" s="8">
         <f>K146&amp;"-"&amp;L146</f>
@@ -8443,10 +8443,10 @@
         <v/>
       </c>
       <c r="K147" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L147" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M147" s="8">
         <f>K147&amp;"-"&amp;L147</f>
@@ -8498,10 +8498,10 @@
         <v/>
       </c>
       <c r="K148" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L148" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M148" s="8">
         <f>K148&amp;"-"&amp;L148</f>
@@ -8553,10 +8553,10 @@
         <v/>
       </c>
       <c r="K149" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L149" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M149" s="8">
         <f>K149&amp;"-"&amp;L149</f>
@@ -8608,10 +8608,10 @@
         <v/>
       </c>
       <c r="K150" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L150" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M150" s="8">
         <f>K150&amp;"-"&amp;L150</f>
@@ -8663,10 +8663,10 @@
         <v/>
       </c>
       <c r="K151" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L151" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M151" s="8">
         <f>K151&amp;"-"&amp;L151</f>
@@ -8718,10 +8718,10 @@
         <v/>
       </c>
       <c r="K152" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L152" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M152" s="8">
         <f>K152&amp;"-"&amp;L152</f>
@@ -8773,10 +8773,10 @@
         <v/>
       </c>
       <c r="K153" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L153" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M153" s="8">
         <f>K153&amp;"-"&amp;L153</f>
@@ -8828,10 +8828,10 @@
         <v/>
       </c>
       <c r="K154" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L154" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M154" s="8">
         <f>K154&amp;"-"&amp;L154</f>
@@ -8883,10 +8883,10 @@
         <v/>
       </c>
       <c r="K155" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L155" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M155" s="8">
         <f>K155&amp;"-"&amp;L155</f>
@@ -8938,10 +8938,10 @@
         <v/>
       </c>
       <c r="K156" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L156" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M156" s="8">
         <f>K156&amp;"-"&amp;L156</f>
@@ -8993,10 +8993,10 @@
         <v/>
       </c>
       <c r="K157" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L157" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M157" s="8">
         <f>K157&amp;"-"&amp;L157</f>
@@ -9048,10 +9048,10 @@
         <v/>
       </c>
       <c r="K158" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L158" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M158" s="8">
         <f>K158&amp;"-"&amp;L158</f>
@@ -9103,10 +9103,10 @@
         <v/>
       </c>
       <c r="K159" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L159" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M159" s="8">
         <f>K159&amp;"-"&amp;L159</f>
@@ -9158,10 +9158,10 @@
         <v/>
       </c>
       <c r="K160" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L160" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M160" s="8">
         <f>K160&amp;"-"&amp;L160</f>
@@ -9213,10 +9213,10 @@
         <v/>
       </c>
       <c r="K161" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L161" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M161" s="8">
         <f>K161&amp;"-"&amp;L161</f>
@@ -9268,10 +9268,10 @@
         <v/>
       </c>
       <c r="K162" s="8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L162" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M162" s="8">
         <f>K162&amp;"-"&amp;L162</f>
@@ -9323,10 +9323,10 @@
         <v/>
       </c>
       <c r="K163" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L163" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M163" s="8">
         <f>K163&amp;"-"&amp;L163</f>
@@ -9378,10 +9378,10 @@
         <v/>
       </c>
       <c r="K164" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L164" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M164" s="8">
         <f>K164&amp;"-"&amp;L164</f>
@@ -9433,10 +9433,10 @@
         <v/>
       </c>
       <c r="K165" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L165" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M165" s="8">
         <f>K165&amp;"-"&amp;L165</f>
@@ -9488,10 +9488,10 @@
         <v/>
       </c>
       <c r="K166" s="8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L166" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M166" s="8">
         <f>K166&amp;"-"&amp;L166</f>
@@ -9543,10 +9543,10 @@
         <v/>
       </c>
       <c r="K167" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L167" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M167" s="8">
         <f>K167&amp;"-"&amp;L167</f>
@@ -9598,10 +9598,10 @@
         <v/>
       </c>
       <c r="K168" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L168" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M168" s="8">
         <f>K168&amp;"-"&amp;L168</f>
@@ -9653,10 +9653,10 @@
         <v/>
       </c>
       <c r="K169" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L169" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M169" s="8">
         <f>K169&amp;"-"&amp;L169</f>
@@ -9708,10 +9708,10 @@
         <v/>
       </c>
       <c r="K170" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L170" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M170" s="8">
         <f>K170&amp;"-"&amp;L170</f>
@@ -9763,10 +9763,10 @@
         <v/>
       </c>
       <c r="K171" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L171" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M171" s="8">
         <f>K171&amp;"-"&amp;L171</f>
@@ -9818,10 +9818,10 @@
         <v/>
       </c>
       <c r="K172" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L172" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M172" s="8">
         <f>K172&amp;"-"&amp;L172</f>
@@ -9873,10 +9873,10 @@
         <v/>
       </c>
       <c r="K173" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L173" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M173" s="8">
         <f>K173&amp;"-"&amp;L173</f>
@@ -9928,10 +9928,10 @@
         <v/>
       </c>
       <c r="K174" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L174" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M174" s="8">
         <f>K174&amp;"-"&amp;L174</f>
@@ -10006,7 +10006,7 @@
     <row r="178">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>Teams with no games vs top 40</t>
+          <t>Teams with no November games vs top 40</t>
         </is>
       </c>
       <c r="B178" s="11" t="n"/>

--- a/reports/upset_high_seeds.xlsx
+++ b/reports/upset_high_seeds.xlsx
@@ -523,23 +523,23 @@
   <dimension ref="A1:N179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="10.9" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17.7" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="40.3" customWidth="1" min="5" max="5"/>
+    <col width="16.7" customWidth="1" min="6" max="6"/>
+    <col width="11.6" customWidth="1" min="7" max="7"/>
+    <col width="9.699999999999999" customWidth="1" min="8" max="8"/>
+    <col width="11.6" customWidth="1" min="9" max="9"/>
+    <col width="15.3" customWidth="1" min="10" max="10"/>
+    <col width="13.6" customWidth="1" min="11" max="11"/>
+    <col width="13.6" customWidth="1" min="12" max="12"/>
+    <col width="15.3" customWidth="1" min="13" max="13"/>
+    <col width="13.6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Higher seeds upset in the NCAA tournament by a team 4+ seed lines worse, 2010–2026</t>
@@ -575,7 +575,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
+    <row r="5" ht="48.75" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Year</t>
@@ -649,39 +649,39 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Final Four</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>UConn</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>97–83</t>
+          <t>63–53</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="8">
         <f>H6&amp;"-"&amp;I6</f>
@@ -691,7 +691,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="8">
         <f>K6&amp;"-"&amp;L6</f>
@@ -704,46 +704,46 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Final Four</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Murray St.</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>66–65</t>
+          <t>74–73</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="8">
         <f>H7&amp;"-"&amp;I7</f>
         <v/>
       </c>
       <c r="K7" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>0</v>
@@ -759,46 +759,46 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Final Four</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Temple</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Cornell</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>78–65</t>
+          <t>81–77</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="8">
         <f>H8&amp;"-"&amp;I8</f>
         <v/>
       </c>
       <c r="K8" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>1</v>
@@ -814,19 +814,19 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Elite Eight</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Notre Dame</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="E9" s="8" t="n">
@@ -834,26 +834,26 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>51–50</t>
+          <t>71–61</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="8">
         <f>H9&amp;"-"&amp;I9</f>
         <v/>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="8" t="n">
         <v>0</v>
@@ -869,36 +869,36 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Elite Eight</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>80–78</t>
+          <t>74–71</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" s="8" t="n">
         <v>1</v>
@@ -908,7 +908,7 @@
         <v/>
       </c>
       <c r="K10" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>1</v>
@@ -924,19 +924,19 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Elite Eight</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Ohio St.</t>
         </is>
       </c>
       <c r="E11" s="8" t="n">
@@ -944,19 +944,19 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>UNI</t>
+          <t>Wichita St.</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>69–67</t>
+          <t>70–66</t>
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="8">
         <f>H11&amp;"-"&amp;I11</f>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="8">
         <f>K11&amp;"-"&amp;L11</f>
@@ -979,11 +979,11 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Elite Eight</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -991,27 +991,27 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Saint Mary's (CA)</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>75–68</t>
+          <t>75–72</t>
         </is>
       </c>
       <c r="H12" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="8">
         <f>H12&amp;"-"&amp;I12</f>
@@ -1021,7 +1021,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="8">
         <f>K12&amp;"-"&amp;L12</f>
@@ -1034,39 +1034,39 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Elite Eight</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>82–64</t>
+          <t>68–62</t>
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="8">
         <f>H13&amp;"-"&amp;I13</f>
@@ -1089,46 +1089,46 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>2010</v>
+        <v>2021</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Elite Eight</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Cornell</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>87–69</t>
+          <t>51–49</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="8">
         <f>H14&amp;"-"&amp;I14</f>
         <v/>
       </c>
       <c r="K14" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="8" t="n">
         <v>0</v>
@@ -1144,39 +1144,39 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>2010</v>
+        <v>2023</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Elite Eight</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>Kansas St.</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Fla. Atlantic</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>63–59</t>
+          <t>79–76</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="8">
         <f>H15&amp;"-"&amp;I15</f>
@@ -1199,39 +1199,39 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Elite Eight</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Ohio St.</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="E16" s="8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>76–73</t>
+          <t>76–64</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="8">
         <f>H16&amp;"-"&amp;I16</f>
@@ -1241,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="8">
         <f>K16&amp;"-"&amp;L16</f>
@@ -1254,32 +1254,32 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Morehead St.</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>62–61</t>
+          <t>63–59</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
@@ -1309,39 +1309,39 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Ohio St.</t>
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>69–66</t>
+          <t>76–73</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="8">
         <f>H18&amp;"-"&amp;I18</f>
@@ -1351,7 +1351,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="8">
         <f>K18&amp;"-"&amp;L18</f>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Duke</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>93–77</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>St. John's (NY)</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Gonzaga</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t>86–71</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>4</v>
-      </c>
       <c r="I19" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="8">
         <f>H19&amp;"-"&amp;I19</f>
         <v/>
       </c>
       <c r="K19" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="8" t="n">
         <v>0</v>
@@ -1423,35 +1423,35 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="E20" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>66–55</t>
+          <t>61–54</t>
         </is>
       </c>
       <c r="H20" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="8">
         <f>H20&amp;"-"&amp;I20</f>
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="8">
         <f>K20&amp;"-"&amp;L20</f>
@@ -1474,32 +1474,32 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>74–56</t>
+          <t>68–58</t>
         </is>
       </c>
       <c r="H21" s="8" t="n">
@@ -1513,7 +1513,7 @@
         <v/>
       </c>
       <c r="K21" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>0</v>
@@ -1529,36 +1529,36 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Iowa St.</t>
         </is>
       </c>
       <c r="E22" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>UConn</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>71–70</t>
+          <t>81–76</t>
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v/>
       </c>
       <c r="K22" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="8" t="n">
         <v>0</v>
@@ -1584,49 +1584,49 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Notre Dame</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Florida St.</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>71–57</t>
+          <t>74–69</t>
         </is>
       </c>
       <c r="H23" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="8">
         <f>H23&amp;"-"&amp;I23</f>
         <v/>
       </c>
       <c r="K23" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="8">
         <f>K23&amp;"-"&amp;L23</f>
@@ -1639,11 +1639,11 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
@@ -1651,27 +1651,27 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="E24" s="8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Michigan St.</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>66–62</t>
+          <t>62–58</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" s="8">
         <f>H24&amp;"-"&amp;I24</f>
@@ -1681,7 +1681,7 @@
         <v>1</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="8">
         <f>K24&amp;"-"&amp;L24</f>
@@ -1694,19 +1694,19 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="E25" s="8" t="n">
@@ -1714,16 +1714,16 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>94–76</t>
+          <t>73–71</t>
         </is>
       </c>
       <c r="H25" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I25" s="8" t="n">
         <v>1</v>
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="8">
         <f>K25&amp;"-"&amp;L25</f>
@@ -1749,7 +1749,7 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -1757,28 +1757,28 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>93–77</t>
+          <t>70–50</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" s="8" t="n">
         <v>0</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
@@ -1816,37 +1816,37 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Florida St.</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>61–54</t>
+          <t>75–60</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" s="8">
         <f>H27&amp;"-"&amp;I27</f>
         <v/>
       </c>
       <c r="K27" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27" s="8">
         <f>K27&amp;"-"&amp;L27</f>
@@ -1859,49 +1859,49 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Elite Eight</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>Kansas St.</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>71–61</t>
+          <t>61–58</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="8">
         <f>H28&amp;"-"&amp;I28</f>
         <v/>
       </c>
       <c r="K28" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="8">
         <f>K28&amp;"-"&amp;L28</f>
@@ -1914,39 +1914,39 @@
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Elite Eight</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="E29" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Loyola Chicago</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>74–71</t>
+          <t>69–68</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="8">
         <f>H29&amp;"-"&amp;I29</f>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="8">
         <f>K29&amp;"-"&amp;L29</f>
@@ -1969,49 +1969,49 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Auburn</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>97–80</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Duke</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Lehigh</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>75–70</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="J30" s="8">
         <f>H30&amp;"-"&amp;I30</f>
         <v/>
       </c>
       <c r="K30" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="8">
         <f>K30&amp;"-"&amp;L30</f>
@@ -2024,11 +2024,11 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -2036,34 +2036,34 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="E31" s="8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Norfolk St.</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>86–84</t>
+          <t>88–78</t>
         </is>
       </c>
       <c r="H31" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I31" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="8">
         <f>H31&amp;"-"&amp;I31</f>
         <v/>
       </c>
       <c r="K31" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="8" t="n">
         <v>0</v>
@@ -2079,49 +2079,49 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Loyola Chicago</t>
         </is>
       </c>
       <c r="E32" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Oregon St.</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>65–60</t>
+          <t>65–58</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I32" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" s="8">
         <f>H32&amp;"-"&amp;I32</f>
         <v/>
       </c>
       <c r="K32" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="8">
         <f>K32&amp;"-"&amp;L32</f>
@@ -2134,49 +2134,49 @@
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>Wichita St.</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>12</v>
-      </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>62–59</t>
+          <t>72–60</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I33" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="8">
         <f>H33&amp;"-"&amp;I33</f>
         <v/>
       </c>
       <c r="K33" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M33" s="8">
         <f>K33&amp;"-"&amp;L33</f>
@@ -2189,49 +2189,49 @@
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Temple</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="E34" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>South Fla.</t>
+          <t>Saint Peter's</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>58–44</t>
+          <t>67–64</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I34" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J34" s="8">
         <f>H34&amp;"-"&amp;I34</f>
         <v/>
       </c>
       <c r="K34" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="8">
         <f>K34&amp;"-"&amp;L34</f>
@@ -2244,39 +2244,39 @@
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>UCLA</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>73–66</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>UNLV</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Colorado</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>68–64</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>8</v>
-      </c>
       <c r="I35" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="8">
         <f>H35&amp;"-"&amp;I35</f>
@@ -2286,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="8">
         <f>K35&amp;"-"&amp;L35</f>
@@ -2299,49 +2299,49 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>San Diego St.</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="E36" s="8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Miami (FL)</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>79–65</t>
+          <t>89–75</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
         <v>7</v>
       </c>
       <c r="I36" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="8">
         <f>H36&amp;"-"&amp;I36</f>
         <v/>
       </c>
       <c r="K36" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" s="8">
         <f>K36&amp;"-"&amp;L36</f>
@@ -2354,36 +2354,36 @@
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>San Diego St.</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>66–63</t>
+          <t>71–64</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37" s="8" t="n">
         <v>1</v>
@@ -2393,7 +2393,7 @@
         <v/>
       </c>
       <c r="K37" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>1</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
@@ -2417,38 +2417,38 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="E38" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Fla. Atlantic</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>68–58</t>
+          <t>62–55</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I38" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="8">
         <f>H38&amp;"-"&amp;I38</f>
         <v/>
       </c>
       <c r="K38" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="8" t="n">
         <v>0</v>
@@ -2464,11 +2464,11 @@
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -2476,37 +2476,37 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>FGCU</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>78–68</t>
+          <t>77–72</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="8">
         <f>H39&amp;"-"&amp;I39</f>
         <v/>
       </c>
       <c r="K39" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="8">
         <f>K39&amp;"-"&amp;L39</f>
@@ -2519,49 +2519,49 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="E40" s="8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>Harvard</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>68–62</t>
+          <t>67–58</t>
         </is>
       </c>
       <c r="H40" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I40" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="8">
         <f>H40&amp;"-"&amp;I40</f>
         <v/>
       </c>
       <c r="K40" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="8">
         <f>K40&amp;"-"&amp;L40</f>
@@ -2574,49 +2574,49 @@
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>2013</v>
+        <v>2026</v>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Kansas St.</t>
+          <t>Iowa St.</t>
         </is>
       </c>
       <c r="E41" s="8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>La Salle</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>63–61</t>
+          <t>76–62</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I41" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="8">
         <f>H41&amp;"-"&amp;I41</f>
         <v/>
       </c>
       <c r="K41" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="8">
         <f>K41&amp;"-"&amp;L41</f>
@@ -2629,39 +2629,39 @@
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>2013</v>
+        <v>2026</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Sweet 16</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>UNLV</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="E42" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>64–61</t>
+          <t>77–71</t>
         </is>
       </c>
       <c r="H42" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I42" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="8">
         <f>H42&amp;"-"&amp;I42</f>
@@ -2684,32 +2684,32 @@
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Oklahoma St.</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>UNI</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>68–55</t>
+          <t>69–67</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="K43" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>0</v>
@@ -2739,49 +2739,49 @@
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="E44" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>Ole Miss</t>
+          <t>Saint Mary's (CA)</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>57–46</t>
+          <t>75–68</t>
         </is>
       </c>
       <c r="H44" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I44" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J44" s="8">
         <f>H44&amp;"-"&amp;I44</f>
         <v/>
       </c>
       <c r="K44" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M44" s="8">
         <f>K44&amp;"-"&amp;L44</f>
@@ -2794,19 +2794,19 @@
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="E45" s="8" t="n">
@@ -2814,19 +2814,19 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>83–63</t>
+          <t>82–64</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" s="8">
         <f>H45&amp;"-"&amp;I45</f>
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="L45" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="8">
         <f>K45&amp;"-"&amp;L45</f>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
@@ -2857,38 +2857,38 @@
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="E46" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>Wichita St.</t>
+          <t>Cornell</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>76–70</t>
+          <t>87–69</t>
         </is>
       </c>
       <c r="H46" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I46" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="8">
         <f>H46&amp;"-"&amp;I46</f>
         <v/>
       </c>
       <c r="K46" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>0</v>
@@ -2904,7 +2904,7 @@
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
@@ -2912,41 +2912,41 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Saint Louis</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="E47" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>74–57</t>
+          <t>71–70</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I47" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" s="8">
         <f>H47&amp;"-"&amp;I47</f>
         <v/>
       </c>
       <c r="K47" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="8">
         <f>K47&amp;"-"&amp;L47</f>
@@ -2959,7 +2959,7 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
@@ -2967,41 +2967,41 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>San Diego St.</t>
+          <t>Notre Dame</t>
         </is>
       </c>
       <c r="E48" s="8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>FGCU</t>
+          <t>Florida St.</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>81–71</t>
+          <t>71–57</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="8">
         <f>H48&amp;"-"&amp;I48</f>
         <v/>
       </c>
       <c r="K48" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="8">
         <f>K48&amp;"-"&amp;L48</f>
@@ -3014,49 +3014,49 @@
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Elite Eight</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Ohio St.</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>Wichita St.</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>70–66</t>
+          <t>66–62</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I49" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="8">
         <f>H49&amp;"-"&amp;I49</f>
         <v/>
       </c>
       <c r="K49" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="8">
         <f>K49&amp;"-"&amp;L49</f>
@@ -3069,11 +3069,11 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -3081,27 +3081,27 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="E50" s="8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>Mercer</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>78–71</t>
+          <t>94–76</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I50" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" s="8">
         <f>H50&amp;"-"&amp;I50</f>
@@ -3111,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" s="8">
         <f>K50&amp;"-"&amp;L50</f>
@@ -3124,49 +3124,49 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>Georgetown</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>NC State</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>66–63</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>Cincinnati</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Harvard</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>61–57</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="I51" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="8">
         <f>H51&amp;"-"&amp;I51</f>
         <v/>
       </c>
       <c r="K51" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="8">
         <f>K51&amp;"-"&amp;L51</f>
@@ -3179,39 +3179,39 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="E52" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>North Dakota St.</t>
+          <t>Wichita St.</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>80–75</t>
+          <t>76–70</t>
         </is>
       </c>
       <c r="H52" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I52" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" s="8">
         <f>H52&amp;"-"&amp;I52</f>
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="8">
         <f>K52&amp;"-"&amp;L52</f>
@@ -3234,19 +3234,19 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>Saint Louis</t>
         </is>
       </c>
       <c r="E53" s="8" t="n">
@@ -3254,26 +3254,26 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>SFA</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>77–75</t>
+          <t>74–57</t>
         </is>
       </c>
       <c r="H53" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I53" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J53" s="8">
         <f>H53&amp;"-"&amp;I53</f>
         <v/>
       </c>
       <c r="K53" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="8" t="n">
         <v>1</v>
@@ -3289,39 +3289,39 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Ohio St.</t>
+          <t>San Diego St.</t>
         </is>
       </c>
       <c r="E54" s="8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>Dayton</t>
+          <t>FGCU</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>60–59</t>
+          <t>81–71</t>
         </is>
       </c>
       <c r="H54" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I54" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="8">
         <f>H54&amp;"-"&amp;I54</f>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="8">
         <f>K54&amp;"-"&amp;L54</f>
@@ -3348,32 +3348,32 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C55" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Wichita St.</t>
         </is>
       </c>
       <c r="E55" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>86–67</t>
+          <t>78–76</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I55" s="8" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="K55" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="8" t="n">
         <v>0</v>
@@ -3407,24 +3407,24 @@
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Wichita St.</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="E56" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>UConn</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>78–76</t>
+          <t>77–65</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
@@ -3438,7 +3438,7 @@
         <v/>
       </c>
       <c r="K56" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="8" t="n">
         <v>0</v>
@@ -3466,37 +3466,37 @@
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="E57" s="8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>UConn</t>
+          <t>Stanford</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>77–65</t>
+          <t>60–57</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I57" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="8">
         <f>H57&amp;"-"&amp;I57</f>
         <v/>
       </c>
       <c r="K57" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="8">
         <f>K57&amp;"-"&amp;L57</f>
@@ -3517,31 +3517,31 @@
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="E58" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>Stanford</t>
+          <t>Dayton</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>60–57</t>
+          <t>55–53</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" s="8">
         <f>H58&amp;"-"&amp;I58</f>
@@ -3551,7 +3551,7 @@
         <v>1</v>
       </c>
       <c r="L58" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="8">
         <f>K58&amp;"-"&amp;L58</f>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
@@ -3572,28 +3572,28 @@
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="E59" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Dayton</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>55–53</t>
+          <t>71–68</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I59" s="8" t="n">
         <v>0</v>
@@ -3619,19 +3619,19 @@
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Iowa St.</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="E60" s="8" t="n">
@@ -3639,16 +3639,16 @@
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>UConn</t>
+          <t>Michigan St.</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>81–76</t>
+          <t>60–54</t>
         </is>
       </c>
       <c r="H60" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I60" s="8" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
         <v/>
       </c>
       <c r="K60" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="8" t="n">
         <v>0</v>
@@ -3674,36 +3674,36 @@
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="E61" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Wichita St.</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>74–69</t>
+          <t>78–65</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I61" s="8" t="n">
         <v>1</v>
@@ -3713,7 +3713,7 @@
         <v/>
       </c>
       <c r="K61" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="8" t="n">
         <v>1</v>
@@ -3729,11 +3729,11 @@
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Elite Eight</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
@@ -3741,27 +3741,27 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="E62" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>75–72</t>
+          <t>66–63</t>
         </is>
       </c>
       <c r="H62" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I62" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J62" s="8">
         <f>H62&amp;"-"&amp;I62</f>
@@ -3771,7 +3771,7 @@
         <v>1</v>
       </c>
       <c r="L62" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="8">
         <f>K62&amp;"-"&amp;L62</f>
@@ -3784,36 +3784,36 @@
     </row>
     <row r="63">
       <c r="A63" s="8" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Final Four</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Utah</t>
         </is>
       </c>
       <c r="E63" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>UConn</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>63–53</t>
+          <t>82–59</t>
         </is>
       </c>
       <c r="H63" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I63" s="8" t="n">
         <v>1</v>
@@ -3823,7 +3823,7 @@
         <v/>
       </c>
       <c r="K63" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="8" t="n">
         <v>1</v>
@@ -3839,19 +3839,19 @@
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Final Four</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="E64" s="8" t="n">
@@ -3859,16 +3859,16 @@
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>74–73</t>
+          <t>65–62</t>
         </is>
       </c>
       <c r="H64" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I64" s="8" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v/>
       </c>
       <c r="K64" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L64" s="8" t="n">
         <v>0</v>
@@ -3894,36 +3894,36 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="E65" s="8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Georgia St.</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>57–56</t>
+          <t>73–69</t>
         </is>
       </c>
       <c r="H65" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I65" s="8" t="n">
         <v>1</v>
@@ -3933,10 +3933,10 @@
         <v/>
       </c>
       <c r="K65" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="8">
         <f>K65&amp;"-"&amp;L65</f>
@@ -3949,36 +3949,36 @@
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Iowa St.</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="E66" s="8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>UAB</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>60–59</t>
+          <t>88–81</t>
         </is>
       </c>
       <c r="H66" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I66" s="8" t="n">
         <v>1</v>
@@ -4004,19 +4004,19 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>Florida St.</t>
         </is>
       </c>
       <c r="E67" s="8" t="n">
@@ -4024,29 +4024,29 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>60–59</t>
+          <t>91–66</t>
         </is>
       </c>
       <c r="H67" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I67" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J67" s="8">
         <f>H67&amp;"-"&amp;I67</f>
         <v/>
       </c>
       <c r="K67" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" s="8">
         <f>K67&amp;"-"&amp;L67</f>
@@ -4059,32 +4059,32 @@
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="E68" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Dayton</t>
+          <t>Florida St.</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>66–53</t>
+          <t>75–70</t>
         </is>
       </c>
       <c r="H68" s="8" t="n">
@@ -4114,7 +4114,7 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
@@ -4122,28 +4122,28 @@
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>71–68</t>
+          <t>75–73</t>
         </is>
       </c>
       <c r="H69" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I69" s="8" t="n">
         <v>0</v>
@@ -4153,7 +4153,7 @@
         <v/>
       </c>
       <c r="K69" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="8" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="E70" s="8" t="n">
@@ -4189,29 +4189,29 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>Michigan St.</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>60–54</t>
+          <t>86–65</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I70" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="8">
         <f>H70&amp;"-"&amp;I70</f>
         <v/>
       </c>
       <c r="K70" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L70" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="8">
         <f>K70&amp;"-"&amp;L70</f>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
@@ -4232,24 +4232,24 @@
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="E71" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>Wichita St.</t>
+          <t>Loyola Chicago</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>78–65</t>
+          <t>63–62</t>
         </is>
       </c>
       <c r="H71" s="8" t="n">
@@ -4263,7 +4263,7 @@
         <v/>
       </c>
       <c r="K71" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="8" t="n">
         <v>1</v>
@@ -4279,11 +4279,11 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
@@ -4291,34 +4291,34 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Michigan St.</t>
         </is>
       </c>
       <c r="E72" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Michigan St.</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>62–58</t>
+          <t>55–53</t>
         </is>
       </c>
       <c r="H72" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I72" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" s="8">
         <f>H72&amp;"-"&amp;I72</f>
         <v/>
       </c>
       <c r="K72" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="8" t="n">
         <v>1</v>
@@ -4334,36 +4334,36 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Michigan St.</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="E73" s="8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>Middle Tenn.</t>
+          <t>Loyola Chicago</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>90–81</t>
+          <t>71–58</t>
         </is>
       </c>
       <c r="H73" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I73" s="8" t="n">
         <v>0</v>
@@ -4373,7 +4373,7 @@
         <v/>
       </c>
       <c r="K73" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="8" t="n">
         <v>0</v>
@@ -4389,36 +4389,36 @@
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="E74" s="8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>SFA</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>70–56</t>
+          <t>95–80</t>
         </is>
       </c>
       <c r="H74" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I74" s="8" t="n">
         <v>0</v>
@@ -4444,39 +4444,39 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="E75" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>77–66</t>
+          <t>75–72</t>
         </is>
       </c>
       <c r="H75" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J75" s="8">
         <f>H75&amp;"-"&amp;I75</f>
@@ -4499,19 +4499,19 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Oklahoma St.</t>
         </is>
       </c>
       <c r="E76" s="8" t="n">
@@ -4519,16 +4519,16 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Little Rock</t>
+          <t>Oregon St.</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>85–83</t>
+          <t>80–70</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I76" s="8" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v/>
       </c>
       <c r="K76" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="8" t="n">
         <v>0</v>
@@ -4554,39 +4554,39 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="E77" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>Oral Roberts</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>79–75</t>
+          <t>81–78</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I77" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" s="8">
         <f>H77&amp;"-"&amp;I77</f>
@@ -4596,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="8">
         <f>K77&amp;"-"&amp;L77</f>
@@ -4609,46 +4609,46 @@
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Seton Hall</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="E78" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>68–52</t>
+          <t>93–86</t>
         </is>
       </c>
       <c r="H78" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I78" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="8">
         <f>H78&amp;"-"&amp;I78</f>
         <v/>
       </c>
       <c r="K78" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="8" t="n">
         <v>0</v>
@@ -4664,36 +4664,36 @@
     </row>
     <row r="79">
       <c r="A79" s="8" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="E79" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Wichita St.</t>
+          <t>Miami (FL)</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>65–55</t>
+          <t>79–61</t>
         </is>
       </c>
       <c r="H79" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I79" s="8" t="n">
         <v>1</v>
@@ -4703,10 +4703,10 @@
         <v/>
       </c>
       <c r="K79" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="8">
         <f>K79&amp;"-"&amp;L79</f>
@@ -4719,19 +4719,19 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="E80" s="8" t="n">
@@ -4739,29 +4739,29 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>UNI</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>75–72</t>
+          <t>76–68</t>
         </is>
       </c>
       <c r="H80" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I80" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J80" s="8">
         <f>H80&amp;"-"&amp;I80</f>
         <v/>
       </c>
       <c r="K80" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80" s="8">
         <f>K80&amp;"-"&amp;L80</f>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
@@ -4782,38 +4782,38 @@
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="E81" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Iowa St.</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>66–63</t>
+          <t>54–49</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I81" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="8">
         <f>H81&amp;"-"&amp;I81</f>
         <v/>
       </c>
       <c r="K81" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L81" s="8" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
     </row>
     <row r="82">
       <c r="A82" s="8" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
@@ -4837,28 +4837,28 @@
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Utah</t>
+          <t>Murray St.</t>
         </is>
       </c>
       <c r="E82" s="8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Saint Peter's</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>82–59</t>
+          <t>70–60</t>
         </is>
       </c>
       <c r="H82" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I82" s="8" t="n">
         <v>1</v>
@@ -4871,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="8">
         <f>K82&amp;"-"&amp;L82</f>
@@ -4884,11 +4884,11 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="n">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Elite Eight</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -4896,24 +4896,24 @@
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="E83" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>68–62</t>
+          <t>72–71</t>
         </is>
       </c>
       <c r="H83" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I83" s="8" t="n">
         <v>1</v>
@@ -4923,10 +4923,10 @@
         <v/>
       </c>
       <c r="K83" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="8">
         <f>K83&amp;"-"&amp;L83</f>
@@ -4939,46 +4939,46 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="E84" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Middle Tenn.</t>
+          <t>Michigan St.</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>81–72</t>
+          <t>69–60</t>
         </is>
       </c>
       <c r="H84" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I84" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" s="8">
         <f>H84&amp;"-"&amp;I84</f>
         <v/>
       </c>
       <c r="K84" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="8" t="n">
         <v>1</v>
@@ -4994,46 +4994,46 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="E85" s="8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Princeton</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>76–65</t>
+          <t>78–63</t>
         </is>
       </c>
       <c r="H85" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I85" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="8">
         <f>H85&amp;"-"&amp;I85</f>
         <v/>
       </c>
       <c r="K85" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="8" t="n">
         <v>0</v>
@@ -5049,39 +5049,39 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="n">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>St. John's (NY)</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>75–66</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>Creighton</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>Rhode Island</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>84–72</t>
-        </is>
-      </c>
-      <c r="H86" s="8" t="n">
-        <v>7</v>
-      </c>
       <c r="I86" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J86" s="8">
         <f>H86&amp;"-"&amp;I86</f>
@@ -5091,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="L86" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" s="8">
         <f>K86&amp;"-"&amp;L86</f>
@@ -5104,46 +5104,46 @@
     </row>
     <row r="87">
       <c r="A87" s="8" t="n">
-        <v>2017</v>
+        <v>2026</v>
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="E87" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>Southern California</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>66–65</t>
+          <t>73–72</t>
         </is>
       </c>
       <c r="H87" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I87" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J87" s="8">
         <f>H87&amp;"-"&amp;I87</f>
         <v/>
       </c>
       <c r="K87" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="8" t="n">
         <v>1</v>
@@ -5159,7 +5159,7 @@
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
-        <v>2017</v>
+        <v>2026</v>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
@@ -5167,31 +5167,31 @@
         </is>
       </c>
       <c r="C88" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="E88" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>65–62</t>
+          <t>74–68</t>
         </is>
       </c>
       <c r="H88" s="8" t="n">
         <v>7</v>
       </c>
       <c r="I88" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="8">
         <f>H88&amp;"-"&amp;I88</f>
@@ -5201,7 +5201,7 @@
         <v>2</v>
       </c>
       <c r="L88" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="8">
         <f>K88&amp;"-"&amp;L88</f>
@@ -5214,49 +5214,49 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="E89" s="8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>73–69</t>
+          <t>97–83</t>
         </is>
       </c>
       <c r="H89" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I89" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" s="8">
         <f>H89&amp;"-"&amp;I89</f>
         <v/>
       </c>
       <c r="K89" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L89" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="8">
         <f>K89&amp;"-"&amp;L89</f>
@@ -5269,36 +5269,36 @@
     </row>
     <row r="90">
       <c r="A90" s="8" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="E90" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Murray St.</t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>88–81</t>
+          <t>66–65</t>
         </is>
       </c>
       <c r="H90" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I90" s="8" t="n">
         <v>1</v>
@@ -5308,10 +5308,10 @@
         <v/>
       </c>
       <c r="K90" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="8">
         <f>K90&amp;"-"&amp;L90</f>
@@ -5324,39 +5324,39 @@
     </row>
     <row r="91">
       <c r="A91" s="8" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Florida St.</t>
+          <t>Temple</t>
         </is>
       </c>
       <c r="E91" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Cornell</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>91–66</t>
+          <t>78–65</t>
         </is>
       </c>
       <c r="H91" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I91" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" s="8">
         <f>H91&amp;"-"&amp;I91</f>
@@ -5366,7 +5366,7 @@
         <v>1</v>
       </c>
       <c r="L91" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="8">
         <f>K91&amp;"-"&amp;L91</f>
@@ -5379,19 +5379,19 @@
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Notre Dame</t>
         </is>
       </c>
       <c r="E92" s="8" t="n">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>73–71</t>
+          <t>51–50</t>
         </is>
       </c>
       <c r="H92" s="8" t="n">
@@ -5421,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="8">
         <f>K92&amp;"-"&amp;L92</f>
@@ -5434,49 +5434,49 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="E93" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>70–50</t>
+          <t>80–78</t>
         </is>
       </c>
       <c r="H93" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I93" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" s="8">
         <f>H93&amp;"-"&amp;I93</f>
         <v/>
       </c>
       <c r="K93" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L93" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="8">
         <f>K93&amp;"-"&amp;L93</f>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
@@ -5497,28 +5497,28 @@
         </is>
       </c>
       <c r="C94" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="E94" s="8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>UMBC</t>
+          <t>Morehead St.</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>74–54</t>
+          <t>62–61</t>
         </is>
       </c>
       <c r="H94" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I94" s="8" t="n">
         <v>0</v>
@@ -5544,7 +5544,7 @@
     </row>
     <row r="95">
       <c r="A95" s="8" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
@@ -5552,41 +5552,41 @@
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="E95" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>89–68</t>
+          <t>69–66</t>
         </is>
       </c>
       <c r="H95" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I95" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J95" s="8">
         <f>H95&amp;"-"&amp;I95</f>
         <v/>
       </c>
       <c r="K95" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M95" s="8">
         <f>K95&amp;"-"&amp;L95</f>
@@ -5599,7 +5599,7 @@
     </row>
     <row r="96">
       <c r="A96" s="8" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
@@ -5607,28 +5607,28 @@
         </is>
       </c>
       <c r="C96" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>St. John's (NY)</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Gonzaga</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>86–71</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>Wichita St.</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>Marshall</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="inlineStr">
-        <is>
-          <t>81–75</t>
-        </is>
-      </c>
-      <c r="H96" s="8" t="n">
-        <v>5</v>
       </c>
       <c r="I96" s="8" t="n">
         <v>1</v>
@@ -5641,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="L96" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="8">
         <f>K96&amp;"-"&amp;L96</f>
@@ -5654,7 +5654,7 @@
     </row>
     <row r="97">
       <c r="A97" s="8" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Miami (FL)</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="E97" s="8" t="n">
@@ -5674,19 +5674,19 @@
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>Loyola Chicago</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>64–62</t>
+          <t>66–55</t>
         </is>
       </c>
       <c r="H97" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I97" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" s="8">
         <f>H97&amp;"-"&amp;I97</f>
@@ -5709,7 +5709,7 @@
     </row>
     <row r="98">
       <c r="A98" s="8" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="E98" s="8" t="n">
@@ -5729,16 +5729,16 @@
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>57–52</t>
+          <t>74–56</t>
         </is>
       </c>
       <c r="H98" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I98" s="8" t="n">
         <v>0</v>
@@ -5748,7 +5748,7 @@
         <v/>
       </c>
       <c r="K98" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="8" t="n">
         <v>0</v>
@@ -5764,27 +5764,27 @@
     </row>
     <row r="99">
       <c r="A99" s="8" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Duke</t>
         </is>
       </c>
       <c r="E99" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>Florida St.</t>
+          <t>Lehigh</t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr">
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="H99" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I99" s="8" t="n">
         <v>1</v>
@@ -5803,7 +5803,7 @@
         <v/>
       </c>
       <c r="K99" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L99" s="8" t="n">
         <v>1</v>
@@ -5819,11 +5819,11 @@
     </row>
     <row r="100">
       <c r="A100" s="8" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
@@ -5831,24 +5831,24 @@
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="E100" s="8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Norfolk St.</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>75–73</t>
+          <t>86–84</t>
         </is>
       </c>
       <c r="H100" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I100" s="8" t="n">
         <v>0</v>
@@ -5858,7 +5858,7 @@
         <v/>
       </c>
       <c r="K100" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="8" t="n">
         <v>0</v>
@@ -5874,49 +5874,49 @@
     </row>
     <row r="101">
       <c r="A101" s="8" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>65–60</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I101" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>North Carolina</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="inlineStr">
-        <is>
-          <t>86–65</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="I101" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="J101" s="8">
         <f>H101&amp;"-"&amp;I101</f>
         <v/>
       </c>
       <c r="K101" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="L101" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="M101" s="8">
         <f>K101&amp;"-"&amp;L101</f>
@@ -5929,49 +5929,49 @@
     </row>
     <row r="102">
       <c r="A102" s="8" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>Wichita St.</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>VCU</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>62–59</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>Tennessee</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>Loyola Chicago</t>
-        </is>
-      </c>
-      <c r="G102" s="8" t="inlineStr">
-        <is>
-          <t>63–62</t>
-        </is>
-      </c>
-      <c r="H102" s="8" t="n">
-        <v>5</v>
-      </c>
       <c r="I102" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J102" s="8">
         <f>H102&amp;"-"&amp;I102</f>
         <v/>
       </c>
       <c r="K102" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="L102" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="M102" s="8">
         <f>K102&amp;"-"&amp;L102</f>
@@ -5984,46 +5984,46 @@
     </row>
     <row r="103">
       <c r="A103" s="8" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>Temple</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>South Fla.</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>58–44</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>Michigan St.</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>Syracuse</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="inlineStr">
-        <is>
-          <t>55–53</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="I103" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J103" s="8">
         <f>H103&amp;"-"&amp;I103</f>
         <v/>
       </c>
       <c r="K103" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L103" s="8" t="n">
         <v>1</v>
@@ -6039,49 +6039,49 @@
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>UNLV</t>
         </is>
       </c>
       <c r="E104" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>Florida St.</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>75–60</t>
+          <t>68–64</t>
         </is>
       </c>
       <c r="H104" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I104" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="8">
         <f>H104&amp;"-"&amp;I104</f>
         <v/>
       </c>
       <c r="K104" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L104" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" s="8">
         <f>K104&amp;"-"&amp;L104</f>
@@ -6094,49 +6094,49 @@
     </row>
     <row r="105">
       <c r="A105" s="8" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>San Diego St.</t>
         </is>
       </c>
       <c r="E105" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>Kansas St.</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>61–58</t>
+          <t>79–65</t>
         </is>
       </c>
       <c r="H105" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J105" s="8">
         <f>H105&amp;"-"&amp;I105</f>
         <v/>
       </c>
       <c r="K105" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M105" s="8">
         <f>K105&amp;"-"&amp;L105</f>
@@ -6149,39 +6149,39 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C106" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="E106" s="8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>Loyola Chicago</t>
+          <t>FGCU</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>69–68</t>
+          <t>78–68</t>
         </is>
       </c>
       <c r="H106" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I106" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="8">
         <f>H106&amp;"-"&amp;I106</f>
@@ -6191,7 +6191,7 @@
         <v>0</v>
       </c>
       <c r="L106" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="8">
         <f>K106&amp;"-"&amp;L106</f>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="107">
       <c r="A107" s="8" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
@@ -6212,28 +6212,28 @@
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Kansas St.</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="E107" s="8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>Harvard</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>70–64</t>
+          <t>68–62</t>
         </is>
       </c>
       <c r="H107" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I107" s="8" t="n">
         <v>0</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
@@ -6267,41 +6267,41 @@
         </is>
       </c>
       <c r="C108" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Kansas St.</t>
         </is>
       </c>
       <c r="E108" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>Murray St.</t>
+          <t>La Salle</t>
         </is>
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>83–64</t>
+          <t>63–61</t>
         </is>
       </c>
       <c r="H108" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I108" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J108" s="8">
         <f>H108&amp;"-"&amp;I108</f>
         <v/>
       </c>
       <c r="K108" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M108" s="8">
         <f>K108&amp;"-"&amp;L108</f>
@@ -6314,7 +6314,7 @@
     </row>
     <row r="109">
       <c r="A109" s="8" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Mississippi St.</t>
+          <t>UNLV</t>
         </is>
       </c>
       <c r="E109" s="8" t="n">
@@ -6334,16 +6334,16 @@
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>California</t>
         </is>
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>80–76</t>
+          <t>64–61</t>
         </is>
       </c>
       <c r="H109" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I109" s="8" t="n">
         <v>1</v>
@@ -6369,7 +6369,7 @@
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Oklahoma St.</t>
         </is>
       </c>
       <c r="E110" s="8" t="n">
@@ -6394,24 +6394,24 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>72–54</t>
+          <t>68–55</t>
         </is>
       </c>
       <c r="H110" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I110" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" s="8">
         <f>H110&amp;"-"&amp;I110</f>
         <v/>
       </c>
       <c r="K110" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L110" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="8">
         <f>K110&amp;"-"&amp;L110</f>
@@ -6424,7 +6424,7 @@
     </row>
     <row r="111">
       <c r="A111" s="8" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
@@ -6432,31 +6432,31 @@
         </is>
       </c>
       <c r="C111" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Iowa St.</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="E111" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>Ohio St.</t>
+          <t>Ole Miss</t>
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>62–59</t>
+          <t>57–46</t>
         </is>
       </c>
       <c r="H111" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I111" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J111" s="8">
         <f>H111&amp;"-"&amp;I111</f>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M111" s="8">
         <f>K111&amp;"-"&amp;L111</f>
@@ -6479,36 +6479,36 @@
     </row>
     <row r="112">
       <c r="A112" s="8" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C112" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="E112" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>83–63</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="n">
         <v>5</v>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>Auburn</t>
-        </is>
-      </c>
-      <c r="G112" s="8" t="inlineStr">
-        <is>
-          <t>97–80</t>
-        </is>
-      </c>
-      <c r="H112" s="8" t="n">
-        <v>6</v>
       </c>
       <c r="I112" s="8" t="n">
         <v>2</v>
@@ -6518,10 +6518,10 @@
         <v/>
       </c>
       <c r="K112" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M112" s="8">
         <f>K112&amp;"-"&amp;L112</f>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="113">
       <c r="A113" s="8" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
@@ -6542,31 +6542,31 @@
         </is>
       </c>
       <c r="C113" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>Duke</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>Mercer</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>78–71</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I113" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>Ohio St.</t>
-        </is>
-      </c>
-      <c r="E113" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
-          <t>Oral Roberts</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr">
-        <is>
-          <t>75–72</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I113" s="8" t="n">
-        <v>0</v>
       </c>
       <c r="J113" s="8">
         <f>H113&amp;"-"&amp;I113</f>
@@ -6576,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="L113" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M113" s="8">
         <f>K113&amp;"-"&amp;L113</f>
@@ -6589,7 +6589,7 @@
     </row>
     <row r="114">
       <c r="A114" s="8" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
@@ -6597,28 +6597,28 @@
         </is>
       </c>
       <c r="C114" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="E114" s="8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>Abilene Christian</t>
+          <t>Harvard</t>
         </is>
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>53–52</t>
+          <t>61–57</t>
         </is>
       </c>
       <c r="H114" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I114" s="8" t="n">
         <v>0</v>
@@ -6644,7 +6644,7 @@
     </row>
     <row r="115">
       <c r="A115" s="8" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
@@ -6652,28 +6652,28 @@
         </is>
       </c>
       <c r="C115" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="E115" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>North Dakota St.</t>
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>78–69</t>
+          <t>80–75</t>
         </is>
       </c>
       <c r="H115" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I115" s="8" t="n">
         <v>1</v>
@@ -6699,7 +6699,7 @@
     </row>
     <row r="116">
       <c r="A116" s="8" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
@@ -6707,41 +6707,41 @@
         </is>
       </c>
       <c r="C116" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="E116" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>SFA</t>
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>62–58</t>
+          <t>77–75</t>
         </is>
       </c>
       <c r="H116" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I116" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J116" s="8">
         <f>H116&amp;"-"&amp;I116</f>
         <v/>
       </c>
       <c r="K116" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="8">
         <f>K116&amp;"-"&amp;L116</f>
@@ -6754,7 +6754,7 @@
     </row>
     <row r="117">
       <c r="A117" s="8" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
@@ -6762,28 +6762,28 @@
         </is>
       </c>
       <c r="C117" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Ohio St.</t>
         </is>
       </c>
       <c r="E117" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>Oregon St.</t>
+          <t>Dayton</t>
         </is>
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>70–56</t>
+          <t>60–59</t>
         </is>
       </c>
       <c r="H117" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I117" s="8" t="n">
         <v>0</v>
@@ -6809,7 +6809,7 @@
     </row>
     <row r="118">
       <c r="A118" s="8" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>San Diego St.</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="E118" s="8" t="n">
@@ -6829,16 +6829,16 @@
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>78–62</t>
+          <t>86–67</t>
         </is>
       </c>
       <c r="H118" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I118" s="8" t="n">
         <v>0</v>
@@ -6864,7 +6864,7 @@
     </row>
     <row r="119">
       <c r="A119" s="8" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
@@ -6872,31 +6872,31 @@
         </is>
       </c>
       <c r="C119" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="E119" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Georgia St.</t>
         </is>
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>73–62</t>
+          <t>57–56</t>
         </is>
       </c>
       <c r="H119" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I119" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" s="8">
         <f>H119&amp;"-"&amp;I119</f>
@@ -6919,39 +6919,39 @@
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C120" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Iowa St.</t>
         </is>
       </c>
       <c r="E120" s="8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>Loyola Chicago</t>
+          <t>UAB</t>
         </is>
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>71–58</t>
+          <t>60–59</t>
         </is>
       </c>
       <c r="H120" s="8" t="n">
         <v>3</v>
       </c>
       <c r="I120" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" s="8">
         <f>H120&amp;"-"&amp;I120</f>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="L120" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="8">
         <f>K120&amp;"-"&amp;L120</f>
@@ -6974,39 +6974,39 @@
     </row>
     <row r="121">
       <c r="A121" s="8" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C121" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="E121" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>95–80</t>
+          <t>60–59</t>
         </is>
       </c>
       <c r="H121" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I121" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J121" s="8">
         <f>H121&amp;"-"&amp;I121</f>
@@ -7016,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M121" s="8">
         <f>K121&amp;"-"&amp;L121</f>
@@ -7029,19 +7029,19 @@
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C122" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="E122" s="8" t="n">
@@ -7049,29 +7049,29 @@
       </c>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>Syracuse</t>
+          <t>Dayton</t>
         </is>
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>75–72</t>
+          <t>66–53</t>
         </is>
       </c>
       <c r="H122" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I122" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" s="8">
         <f>H122&amp;"-"&amp;I122</f>
         <v/>
       </c>
       <c r="K122" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="8">
         <f>K122&amp;"-"&amp;L122</f>
@@ -7084,36 +7084,36 @@
     </row>
     <row r="123">
       <c r="A123" s="8" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C123" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Oklahoma St.</t>
+          <t>Michigan St.</t>
         </is>
       </c>
       <c r="E123" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>Oregon St.</t>
+          <t>Middle Tenn.</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>80–70</t>
+          <t>90–81</t>
         </is>
       </c>
       <c r="H123" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I123" s="8" t="n">
         <v>0</v>
@@ -7123,7 +7123,7 @@
         <v/>
       </c>
       <c r="K123" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="8" t="n">
         <v>0</v>
@@ -7139,36 +7139,36 @@
     </row>
     <row r="124">
       <c r="A124" s="8" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C124" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="E124" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>Oral Roberts</t>
+          <t>SFA</t>
         </is>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>81–78</t>
+          <t>70–56</t>
         </is>
       </c>
       <c r="H124" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I124" s="8" t="n">
         <v>0</v>
@@ -7194,39 +7194,39 @@
     </row>
     <row r="125">
       <c r="A125" s="8" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C125" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>77–66</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I125" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="D125" s="9" t="inlineStr">
-        <is>
-          <t>Alabama</t>
-        </is>
-      </c>
-      <c r="E125" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F125" s="9" t="inlineStr">
-        <is>
-          <t>UCLA</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr">
-        <is>
-          <t>88–78</t>
-        </is>
-      </c>
-      <c r="H125" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I125" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="J125" s="8">
         <f>H125&amp;"-"&amp;I125</f>
@@ -7249,19 +7249,19 @@
     </row>
     <row r="126">
       <c r="A126" s="8" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C126" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Loyola Chicago</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="E126" s="8" t="n">
@@ -7269,16 +7269,16 @@
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>Oregon St.</t>
+          <t>Little Rock</t>
         </is>
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>65–58</t>
+          <t>85–83</t>
         </is>
       </c>
       <c r="H126" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I126" s="8" t="n">
         <v>0</v>
@@ -7288,7 +7288,7 @@
         <v/>
       </c>
       <c r="K126" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="8" t="n">
         <v>0</v>
@@ -7304,39 +7304,39 @@
     </row>
     <row r="127">
       <c r="A127" s="8" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Elite Eight</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C127" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="E127" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>51–49</t>
+          <t>79–75</t>
         </is>
       </c>
       <c r="H127" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I127" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" s="8">
         <f>H127&amp;"-"&amp;I127</f>
@@ -7346,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="8">
         <f>K127&amp;"-"&amp;L127</f>
@@ -7359,7 +7359,7 @@
     </row>
     <row r="128">
       <c r="A128" s="8" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
@@ -7367,28 +7367,28 @@
         </is>
       </c>
       <c r="C128" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Seton Hall</t>
         </is>
       </c>
       <c r="E128" s="8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>Saint Peter's</t>
+          <t>Gonzaga</t>
         </is>
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>85–79</t>
+          <t>68–52</t>
         </is>
       </c>
       <c r="H128" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I128" s="8" t="n">
         <v>1</v>
@@ -7401,7 +7401,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="8">
         <f>K128&amp;"-"&amp;L128</f>
@@ -7414,7 +7414,7 @@
     </row>
     <row r="129">
       <c r="A129" s="8" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
@@ -7422,28 +7422,28 @@
         </is>
       </c>
       <c r="C129" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>UConn</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="E129" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>New Mexico St.</t>
+          <t>Wichita St.</t>
         </is>
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>70–63</t>
+          <t>65–55</t>
         </is>
       </c>
       <c r="H129" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I129" s="8" t="n">
         <v>1</v>
@@ -7453,10 +7453,10 @@
         <v/>
       </c>
       <c r="K129" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M129" s="8">
         <f>K129&amp;"-"&amp;L129</f>
@@ -7469,7 +7469,7 @@
     </row>
     <row r="130">
       <c r="A130" s="8" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
@@ -7477,31 +7477,31 @@
         </is>
       </c>
       <c r="C130" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="E130" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F130" s="9" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>UNI</t>
         </is>
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>67–63</t>
+          <t>75–72</t>
         </is>
       </c>
       <c r="H130" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I130" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J130" s="8">
         <f>H130&amp;"-"&amp;I130</f>
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M130" s="8">
         <f>K130&amp;"-"&amp;L130</f>
@@ -7524,7 +7524,7 @@
     </row>
     <row r="131">
       <c r="A131" s="8" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
@@ -7532,31 +7532,31 @@
         </is>
       </c>
       <c r="C131" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>Middle Tenn.</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>81–72</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D131" s="9" t="inlineStr">
-        <is>
-          <t>Colorado St.</t>
-        </is>
-      </c>
-      <c r="E131" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F131" s="9" t="inlineStr">
-        <is>
-          <t>Michigan</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr">
-        <is>
-          <t>75–63</t>
-        </is>
-      </c>
-      <c r="H131" s="8" t="n">
-        <v>7</v>
-      </c>
       <c r="I131" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131" s="8">
         <f>H131&amp;"-"&amp;I131</f>
@@ -7566,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="L131" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="8">
         <f>K131&amp;"-"&amp;L131</f>
@@ -7579,7 +7579,7 @@
     </row>
     <row r="132">
       <c r="A132" s="8" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="E132" s="8" t="n">
@@ -7599,26 +7599,26 @@
       </c>
       <c r="F132" s="9" t="inlineStr">
         <is>
-          <t>Iowa St.</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>59–54</t>
+          <t>76–65</t>
         </is>
       </c>
       <c r="H132" s="8" t="n">
         <v>7</v>
       </c>
       <c r="I132" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" s="8">
         <f>H132&amp;"-"&amp;I132</f>
         <v/>
       </c>
       <c r="K132" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="8" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="133">
       <c r="A133" s="8" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Creighton</t>
         </is>
       </c>
       <c r="E133" s="8" t="n">
@@ -7654,26 +7654,26 @@
       </c>
       <c r="F133" s="9" t="inlineStr">
         <is>
-          <t>Notre Dame</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>78–64</t>
+          <t>84–72</t>
         </is>
       </c>
       <c r="H133" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I133" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J133" s="8">
         <f>H133&amp;"-"&amp;I133</f>
         <v/>
       </c>
       <c r="K133" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="8" t="n">
         <v>0</v>
@@ -7689,49 +7689,49 @@
     </row>
     <row r="134">
       <c r="A134" s="8" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C134" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="E134" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Southern California</t>
         </is>
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>93–86</t>
+          <t>66–65</t>
         </is>
       </c>
       <c r="H134" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I134" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J134" s="8">
         <f>H134&amp;"-"&amp;I134</f>
         <v/>
       </c>
       <c r="K134" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L134" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="8">
         <f>K134&amp;"-"&amp;L134</f>
@@ -7744,49 +7744,49 @@
     </row>
     <row r="135">
       <c r="A135" s="8" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C135" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="E135" s="8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>Miami (FL)</t>
+          <t>UMBC</t>
         </is>
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>79–61</t>
+          <t>74–54</t>
         </is>
       </c>
       <c r="H135" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I135" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135" s="8">
         <f>H135&amp;"-"&amp;I135</f>
         <v/>
       </c>
       <c r="K135" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M135" s="8">
         <f>K135&amp;"-"&amp;L135</f>
@@ -7799,49 +7799,49 @@
     </row>
     <row r="136">
       <c r="A136" s="8" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C136" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>Buffalo</t>
+        </is>
+      </c>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t>89–68</t>
+        </is>
+      </c>
+      <c r="H136" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I136" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="D136" s="9" t="inlineStr">
-        <is>
-          <t>Tennessee</t>
-        </is>
-      </c>
-      <c r="E136" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F136" s="9" t="inlineStr">
-        <is>
-          <t>Michigan</t>
-        </is>
-      </c>
-      <c r="G136" s="8" t="inlineStr">
-        <is>
-          <t>76–68</t>
-        </is>
-      </c>
-      <c r="H136" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I136" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="J136" s="8">
         <f>H136&amp;"-"&amp;I136</f>
         <v/>
       </c>
       <c r="K136" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M136" s="8">
         <f>K136&amp;"-"&amp;L136</f>
@@ -7854,32 +7854,32 @@
     </row>
     <row r="137">
       <c r="A137" s="8" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C137" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Wichita St.</t>
         </is>
       </c>
       <c r="E137" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F137" s="9" t="inlineStr">
         <is>
-          <t>Iowa St.</t>
+          <t>Marshall</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>54–49</t>
+          <t>81–75</t>
         </is>
       </c>
       <c r="H137" s="8" t="n">
@@ -7893,10 +7893,10 @@
         <v/>
       </c>
       <c r="K137" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L137" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" s="8">
         <f>K137&amp;"-"&amp;L137</f>
@@ -7909,39 +7909,39 @@
     </row>
     <row r="138">
       <c r="A138" s="8" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C138" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>Murray St.</t>
+          <t>Miami (FL)</t>
         </is>
       </c>
       <c r="E138" s="8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F138" s="9" t="inlineStr">
         <is>
-          <t>Saint Peter's</t>
+          <t>Loyola Chicago</t>
         </is>
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>70–60</t>
+          <t>64–62</t>
         </is>
       </c>
       <c r="H138" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I138" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J138" s="8">
         <f>H138&amp;"-"&amp;I138</f>
@@ -7964,36 +7964,36 @@
     </row>
     <row r="139">
       <c r="A139" s="8" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="E139" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>72–60</t>
+          <t>57–52</t>
         </is>
       </c>
       <c r="H139" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I139" s="8" t="n">
         <v>0</v>
@@ -8003,7 +8003,7 @@
         <v/>
       </c>
       <c r="K139" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" s="8" t="n">
         <v>0</v>
@@ -8019,36 +8019,36 @@
     </row>
     <row r="140">
       <c r="A140" s="8" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C140" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Kansas St.</t>
         </is>
       </c>
       <c r="E140" s="8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F140" s="9" t="inlineStr">
         <is>
-          <t>Saint Peter's</t>
+          <t>UC Irvine</t>
         </is>
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>67–64</t>
+          <t>70–64</t>
         </is>
       </c>
       <c r="H140" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I140" s="8" t="n">
         <v>0</v>
@@ -8058,7 +8058,7 @@
         <v/>
       </c>
       <c r="K140" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L140" s="8" t="n">
         <v>0</v>
@@ -8074,39 +8074,39 @@
     </row>
     <row r="141">
       <c r="A141" s="8" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C141" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="E141" s="8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Murray St.</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>73–66</t>
+          <t>83–64</t>
         </is>
       </c>
       <c r="H141" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I141" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J141" s="8">
         <f>H141&amp;"-"&amp;I141</f>
@@ -8116,7 +8116,7 @@
         <v>1</v>
       </c>
       <c r="L141" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M141" s="8">
         <f>K141&amp;"-"&amp;L141</f>
@@ -8129,36 +8129,36 @@
     </row>
     <row r="142">
       <c r="A142" s="8" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>Final Four</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C142" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Mississippi St.</t>
         </is>
       </c>
       <c r="E142" s="8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F142" s="9" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>81–77</t>
+          <t>80–76</t>
         </is>
       </c>
       <c r="H142" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I142" s="8" t="n">
         <v>1</v>
@@ -8168,10 +8168,10 @@
         <v/>
       </c>
       <c r="K142" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L142" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M142" s="8">
         <f>K142&amp;"-"&amp;L142</f>
@@ -8184,7 +8184,7 @@
     </row>
     <row r="143">
       <c r="A143" s="8" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
@@ -8192,41 +8192,41 @@
         </is>
       </c>
       <c r="C143" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="E143" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F143" s="9" t="inlineStr">
         <is>
-          <t>FDU</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>63–58</t>
+          <t>72–54</t>
         </is>
       </c>
       <c r="H143" s="8" t="n">
         <v>7</v>
       </c>
       <c r="I143" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" s="8">
         <f>H143&amp;"-"&amp;I143</f>
         <v/>
       </c>
       <c r="K143" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L143" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" s="8">
         <f>K143&amp;"-"&amp;L143</f>
@@ -8239,7 +8239,7 @@
     </row>
     <row r="144">
       <c r="A144" s="8" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
@@ -8247,38 +8247,38 @@
         </is>
       </c>
       <c r="C144" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Iowa St.</t>
         </is>
       </c>
       <c r="E144" s="8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F144" s="9" t="inlineStr">
         <is>
-          <t>Princeton</t>
+          <t>Ohio St.</t>
         </is>
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>59–55</t>
+          <t>62–59</t>
         </is>
       </c>
       <c r="H144" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I144" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" s="8">
         <f>H144&amp;"-"&amp;I144</f>
         <v/>
       </c>
       <c r="K144" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L144" s="8" t="n">
         <v>0</v>
@@ -8294,7 +8294,7 @@
     </row>
     <row r="145">
       <c r="A145" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
@@ -8302,28 +8302,28 @@
         </is>
       </c>
       <c r="C145" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Ohio St.</t>
         </is>
       </c>
       <c r="E145" s="8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>Furman</t>
+          <t>Oral Roberts</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>68–67</t>
+          <t>75–72</t>
         </is>
       </c>
       <c r="H145" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I145" s="8" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
         <v/>
       </c>
       <c r="K145" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L145" s="8" t="n">
         <v>0</v>
@@ -8349,7 +8349,7 @@
     </row>
     <row r="146">
       <c r="A146" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
@@ -8357,41 +8357,41 @@
         </is>
       </c>
       <c r="C146" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>Iowa St.</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="E146" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F146" s="9" t="inlineStr">
         <is>
-          <t>Pittsburgh</t>
+          <t>Abilene Christian</t>
         </is>
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>59–41</t>
+          <t>53–52</t>
         </is>
       </c>
       <c r="H146" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" s="8">
         <f>H146&amp;"-"&amp;I146</f>
         <v/>
       </c>
       <c r="K146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L146" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" s="8">
         <f>K146&amp;"-"&amp;L146</f>
@@ -8404,36 +8404,36 @@
     </row>
     <row r="147">
       <c r="A147" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="E147" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F147" s="9" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>72–71</t>
+          <t>78–69</t>
         </is>
       </c>
       <c r="H147" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I147" s="8" t="n">
         <v>1</v>
@@ -8443,7 +8443,7 @@
         <v/>
       </c>
       <c r="K147" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" s="8" t="n">
         <v>1</v>
@@ -8459,49 +8459,49 @@
     </row>
     <row r="148">
       <c r="A148" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C148" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="E148" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F148" s="9" t="inlineStr">
         <is>
-          <t>Michigan St.</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>69–60</t>
+          <t>62–58</t>
         </is>
       </c>
       <c r="H148" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I148" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J148" s="8">
         <f>H148&amp;"-"&amp;I148</f>
         <v/>
       </c>
       <c r="K148" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L148" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" s="8">
         <f>K148&amp;"-"&amp;L148</f>
@@ -8514,36 +8514,36 @@
     </row>
     <row r="149">
       <c r="A149" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C149" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="E149" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F149" s="9" t="inlineStr">
         <is>
-          <t>Princeton</t>
+          <t>Oregon St.</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>78–63</t>
+          <t>70–56</t>
         </is>
       </c>
       <c r="H149" s="8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I149" s="8" t="n">
         <v>0</v>
@@ -8569,36 +8569,36 @@
     </row>
     <row r="150">
       <c r="A150" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C150" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>San Diego St.</t>
         </is>
       </c>
       <c r="E150" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F150" s="9" t="inlineStr">
         <is>
-          <t>Miami (FL)</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>89–75</t>
+          <t>78–62</t>
         </is>
       </c>
       <c r="H150" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I150" s="8" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
         <v/>
       </c>
       <c r="K150" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" s="8" t="n">
         <v>0</v>
@@ -8624,49 +8624,49 @@
     </row>
     <row r="151">
       <c r="A151" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C151" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="E151" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F151" s="9" t="inlineStr">
         <is>
-          <t>San Diego St.</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>71–64</t>
+          <t>73–62</t>
         </is>
       </c>
       <c r="H151" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I151" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" s="8">
         <f>H151&amp;"-"&amp;I151</f>
         <v/>
       </c>
       <c r="K151" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L151" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" s="8">
         <f>K151&amp;"-"&amp;L151</f>
@@ -8679,32 +8679,32 @@
     </row>
     <row r="152">
       <c r="A152" s="8" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C152" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="E152" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F152" s="9" t="inlineStr">
         <is>
-          <t>Fla. Atlantic</t>
+          <t>Saint Peter's</t>
         </is>
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>62–55</t>
+          <t>85–79</t>
         </is>
       </c>
       <c r="H152" s="8" t="n">
@@ -8718,10 +8718,10 @@
         <v/>
       </c>
       <c r="K152" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" s="8">
         <f>K152&amp;"-"&amp;L152</f>
@@ -8734,36 +8734,36 @@
     </row>
     <row r="153">
       <c r="A153" s="8" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>Elite Eight</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C153" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>Kansas St.</t>
+          <t>UConn</t>
         </is>
       </c>
       <c r="E153" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F153" s="9" t="inlineStr">
         <is>
-          <t>Fla. Atlantic</t>
+          <t>New Mexico St.</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>79–76</t>
+          <t>70–63</t>
         </is>
       </c>
       <c r="H153" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I153" s="8" t="n">
         <v>1</v>
@@ -8773,10 +8773,10 @@
         <v/>
       </c>
       <c r="K153" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M153" s="8">
         <f>K153&amp;"-"&amp;L153</f>
@@ -8789,7 +8789,7 @@
     </row>
     <row r="154">
       <c r="A154" s="8" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
@@ -8797,31 +8797,31 @@
         </is>
       </c>
       <c r="C154" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="E154" s="8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F154" s="9" t="inlineStr">
         <is>
-          <t>Oakland</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>80–76</t>
+          <t>67–63</t>
         </is>
       </c>
       <c r="H154" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I154" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" s="8">
         <f>H154&amp;"-"&amp;I154</f>
@@ -8831,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" s="8">
         <f>K154&amp;"-"&amp;L154</f>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="155">
       <c r="A155" s="8" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
@@ -8852,31 +8852,31 @@
         </is>
       </c>
       <c r="C155" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>Colorado St.</t>
         </is>
       </c>
       <c r="E155" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>Yale</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>78–76</t>
+          <t>75–63</t>
         </is>
       </c>
       <c r="H155" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I155" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J155" s="8">
         <f>H155&amp;"-"&amp;I155</f>
@@ -8886,7 +8886,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" s="8">
         <f>K155&amp;"-"&amp;L155</f>
@@ -8899,7 +8899,7 @@
     </row>
     <row r="156">
       <c r="A156" s="8" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
@@ -8907,41 +8907,41 @@
         </is>
       </c>
       <c r="C156" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>Saint Mary's (CA)</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="E156" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F156" s="9" t="inlineStr">
         <is>
-          <t>Grand Canyon</t>
+          <t>Iowa St.</t>
         </is>
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>75–66</t>
+          <t>59–54</t>
         </is>
       </c>
       <c r="H156" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I156" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J156" s="8">
         <f>H156&amp;"-"&amp;I156</f>
         <v/>
       </c>
       <c r="K156" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L156" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="8">
         <f>K156&amp;"-"&amp;L156</f>
@@ -8954,7 +8954,7 @@
     </row>
     <row r="157">
       <c r="A157" s="8" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
@@ -8962,31 +8962,31 @@
         </is>
       </c>
       <c r="C157" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="E157" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F157" s="9" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Notre Dame</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>72–61</t>
+          <t>78–64</t>
         </is>
       </c>
       <c r="H157" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I157" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J157" s="8">
         <f>H157&amp;"-"&amp;I157</f>
@@ -8996,7 +8996,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" s="8">
         <f>K157&amp;"-"&amp;L157</f>
@@ -9009,7 +9009,7 @@
     </row>
     <row r="158">
       <c r="A158" s="8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
@@ -9017,28 +9017,28 @@
         </is>
       </c>
       <c r="C158" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="E158" s="8" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>Duquesne</t>
+          <t>FDU</t>
         </is>
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>71–67</t>
+          <t>63–58</t>
         </is>
       </c>
       <c r="H158" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I158" s="8" t="n">
         <v>0</v>
@@ -9048,7 +9048,7 @@
         <v/>
       </c>
       <c r="K158" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L158" s="8" t="n">
         <v>0</v>
@@ -9064,7 +9064,7 @@
     </row>
     <row r="159">
       <c r="A159" s="8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
@@ -9072,41 +9072,41 @@
         </is>
       </c>
       <c r="C159" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>Princeton</t>
+        </is>
+      </c>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t>59–55</t>
+        </is>
+      </c>
+      <c r="H159" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D159" s="9" t="inlineStr">
-        <is>
-          <t>Texas Tech</t>
-        </is>
-      </c>
-      <c r="E159" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F159" s="9" t="inlineStr">
-        <is>
-          <t>NC State</t>
-        </is>
-      </c>
-      <c r="G159" s="8" t="inlineStr">
-        <is>
-          <t>80–67</t>
-        </is>
-      </c>
-      <c r="H159" s="8" t="n">
-        <v>5</v>
-      </c>
       <c r="I159" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J159" s="8">
         <f>H159&amp;"-"&amp;I159</f>
         <v/>
       </c>
       <c r="K159" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L159" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M159" s="8">
         <f>K159&amp;"-"&amp;L159</f>
@@ -9119,7 +9119,7 @@
     </row>
     <row r="160">
       <c r="A160" s="8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
@@ -9127,24 +9127,24 @@
         </is>
       </c>
       <c r="C160" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="E160" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F160" s="9" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Furman</t>
         </is>
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>87–73</t>
+          <t>68–67</t>
         </is>
       </c>
       <c r="H160" s="8" t="n">
@@ -9158,7 +9158,7 @@
         <v/>
       </c>
       <c r="K160" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L160" s="8" t="n">
         <v>0</v>
@@ -9174,49 +9174,49 @@
     </row>
     <row r="161">
       <c r="A161" s="8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C161" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Iowa St.</t>
         </is>
       </c>
       <c r="E161" s="8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Pittsburgh</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>77–72</t>
+          <t>59–41</t>
         </is>
       </c>
       <c r="H161" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I161" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J161" s="8">
         <f>H161&amp;"-"&amp;I161</f>
         <v/>
       </c>
       <c r="K161" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L161" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M161" s="8">
         <f>K161&amp;"-"&amp;L161</f>
@@ -9233,28 +9233,28 @@
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C162" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="E162" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F162" s="9" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Oakland</t>
         </is>
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>67–58</t>
+          <t>80–76</t>
         </is>
       </c>
       <c r="H162" s="8" t="n">
@@ -9268,7 +9268,7 @@
         <v/>
       </c>
       <c r="K162" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L162" s="8" t="n">
         <v>1</v>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>Elite Eight</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C163" s="8" t="n">
@@ -9296,34 +9296,34 @@
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>Duke</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="E163" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Yale</t>
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>76–64</t>
+          <t>78–76</t>
         </is>
       </c>
       <c r="H163" s="8" t="n">
         <v>5</v>
       </c>
       <c r="I163" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J163" s="8">
         <f>H163&amp;"-"&amp;I163</f>
         <v/>
       </c>
       <c r="K163" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L163" s="8" t="n">
         <v>1</v>
@@ -9339,7 +9339,7 @@
     </row>
     <row r="164">
       <c r="A164" s="8" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Saint Mary's (CA)</t>
         </is>
       </c>
       <c r="E164" s="8" t="n">
@@ -9359,29 +9359,29 @@
       </c>
       <c r="F164" s="9" t="inlineStr">
         <is>
-          <t>McNeese</t>
+          <t>Grand Canyon</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>69–67</t>
+          <t>75–66</t>
         </is>
       </c>
       <c r="H164" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I164" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J164" s="8">
         <f>H164&amp;"-"&amp;I164</f>
         <v/>
       </c>
       <c r="K164" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L164" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" s="8">
         <f>K164&amp;"-"&amp;L164</f>
@@ -9394,7 +9394,7 @@
     </row>
     <row r="165">
       <c r="A165" s="8" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>Memphis</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="E165" s="8" t="n">
@@ -9414,26 +9414,26 @@
       </c>
       <c r="F165" s="9" t="inlineStr">
         <is>
-          <t>Colorado St.</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>78–70</t>
+          <t>72–61</t>
         </is>
       </c>
       <c r="H165" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I165" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J165" s="8">
         <f>H165&amp;"-"&amp;I165</f>
         <v/>
       </c>
       <c r="K165" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L165" s="8" t="n">
         <v>1</v>
@@ -9449,7 +9449,7 @@
     </row>
     <row r="166">
       <c r="A166" s="8" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="E166" s="8" t="n">
@@ -9469,26 +9469,26 @@
       </c>
       <c r="F166" s="9" t="inlineStr">
         <is>
-          <t>Drake</t>
+          <t>Duquesne</t>
         </is>
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>67–57</t>
+          <t>71–67</t>
         </is>
       </c>
       <c r="H166" s="8" t="n">
         <v>6</v>
       </c>
       <c r="I166" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J166" s="8">
         <f>H166&amp;"-"&amp;I166</f>
         <v/>
       </c>
       <c r="K166" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" s="8" t="n">
         <v>0</v>
@@ -9504,36 +9504,36 @@
     </row>
     <row r="167">
       <c r="A167" s="8" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>St. John's (NY)</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="E167" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>75–66</t>
+          <t>80–67</t>
         </is>
       </c>
       <c r="H167" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I167" s="8" t="n">
         <v>2</v>
@@ -9543,10 +9543,10 @@
         <v/>
       </c>
       <c r="K167" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L167" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M167" s="8">
         <f>K167&amp;"-"&amp;L167</f>
@@ -9559,7 +9559,7 @@
     </row>
     <row r="168">
       <c r="A168" s="8" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
@@ -9567,31 +9567,31 @@
         </is>
       </c>
       <c r="C168" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="E168" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F168" s="9" t="inlineStr">
         <is>
-          <t>High Point</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>83–82</t>
+          <t>87–73</t>
         </is>
       </c>
       <c r="H168" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I168" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J168" s="8">
         <f>H168&amp;"-"&amp;I168</f>
@@ -9601,7 +9601,7 @@
         <v>0</v>
       </c>
       <c r="L168" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" s="8">
         <f>K168&amp;"-"&amp;L168</f>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="169">
       <c r="A169" s="8" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
@@ -9622,28 +9622,28 @@
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Clemson</t>
         </is>
       </c>
       <c r="E169" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>McNeese</t>
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t>79–71</t>
+          <t>69–67</t>
         </is>
       </c>
       <c r="H169" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I169" s="8" t="n">
         <v>1</v>
@@ -9653,10 +9653,10 @@
         <v/>
       </c>
       <c r="K169" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L169" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M169" s="8">
         <f>K169&amp;"-"&amp;L169</f>
@@ -9669,7 +9669,7 @@
     </row>
     <row r="170">
       <c r="A170" s="8" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
@@ -9677,24 +9677,24 @@
         </is>
       </c>
       <c r="C170" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="E170" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F170" s="9" t="inlineStr">
         <is>
-          <t>VCU</t>
+          <t>Colorado St.</t>
         </is>
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>82–78</t>
+          <t>78–70</t>
         </is>
       </c>
       <c r="H170" s="8" t="n">
@@ -9708,7 +9708,7 @@
         <v/>
       </c>
       <c r="K170" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L170" s="8" t="n">
         <v>1</v>
@@ -9724,49 +9724,49 @@
     </row>
     <row r="171">
       <c r="A171" s="8" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="E171" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Drake</t>
         </is>
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>73–72</t>
+          <t>67–57</t>
         </is>
       </c>
       <c r="H171" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I171" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J171" s="8">
         <f>H171&amp;"-"&amp;I171</f>
         <v/>
       </c>
       <c r="K171" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L171" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M171" s="8">
         <f>K171&amp;"-"&amp;L171</f>
@@ -9783,42 +9783,42 @@
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C172" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>Gonzaga</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="E172" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F172" s="9" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>High Point</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>74–68</t>
+          <t>83–82</t>
         </is>
       </c>
       <c r="H172" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I172" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J172" s="8">
         <f>H172&amp;"-"&amp;I172</f>
         <v/>
       </c>
       <c r="K172" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L172" s="8" t="n">
         <v>1</v>
@@ -9838,45 +9838,45 @@
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>Iowa St.</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="E173" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F173" s="9" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
+          <t>79–71</t>
+        </is>
+      </c>
+      <c r="H173" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F173" s="9" t="inlineStr">
-        <is>
-          <t>Tennessee</t>
-        </is>
-      </c>
-      <c r="G173" s="8" t="inlineStr">
-        <is>
-          <t>76–62</t>
-        </is>
-      </c>
-      <c r="H173" s="8" t="n">
-        <v>7</v>
-      </c>
       <c r="I173" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J173" s="8">
         <f>H173&amp;"-"&amp;I173</f>
         <v/>
       </c>
       <c r="K173" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L173" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M173" s="8">
         <f>K173&amp;"-"&amp;L173</f>
@@ -9893,35 +9893,35 @@
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>Sweet 16</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="C174" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="E174" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F174" s="9" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>VCU</t>
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>77–71</t>
+          <t>82–78</t>
         </is>
       </c>
       <c r="H174" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I174" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J174" s="8">
         <f>H174&amp;"-"&amp;I174</f>
@@ -9931,7 +9931,7 @@
         <v>1</v>
       </c>
       <c r="L174" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M174" s="8">
         <f>K174&amp;"-"&amp;L174</f>
